--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9366A3-786B-41EC-83B5-EBAD0C6E2ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBA4E05-3500-4A6C-AE15-B1C4B51ACED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="160">
   <si>
     <t>ID</t>
   </si>
@@ -504,13 +504,28 @@
   </si>
   <si>
     <t>Organizzazioni_collegate</t>
+  </si>
+  <si>
+    <t>Nome_file</t>
+  </si>
+  <si>
+    <t>Delegazione PCd'I.jpg</t>
+  </si>
+  <si>
+    <t>1968.08.31, pag. 4 - Pesce e Mao.jpg</t>
+  </si>
+  <si>
+    <t>Renmin Ribao - 3 ottobre 1969, p.1 - Fosco Dinucci ai festeggiamenti RPC.jpg</t>
+  </si>
+  <si>
+    <t>Delegazione, ministero degli esteri.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,6 +555,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -562,18 +583,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -606,12 +642,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:M32" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:M32" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M31">
-    <sortCondition ref="A1:A31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:N32" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:N32" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N32">
+    <sortCondition ref="F1:F32"/>
   </sortState>
-  <tableColumns count="13">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{2154B3EB-64E4-4E6D-8A0C-04D65D066E62}" name="ID"/>
     <tableColumn id="2" xr3:uid="{7C80280B-722C-4CED-A5F4-3F72F39F1DFC}" name="Titolo"/>
     <tableColumn id="3" xr3:uid="{42E23130-656A-4022-81E0-AF9117BAC245}" name="Organizzazione"/>
@@ -625,6 +661,7 @@
     <tableColumn id="9" xr3:uid="{18ED1BDE-DA2B-4274-908B-BC06AD7B6402}" name="Keywords"/>
     <tableColumn id="10" xr3:uid="{AEDEDEC1-9395-48B6-A4EF-01A581661641}" name="Note"/>
     <tableColumn id="11" xr3:uid="{575D6553-9BD2-40E4-8055-A706418FDCC7}" name="URL" dataCellStyle="Collegamento ipertestuale"/>
+    <tableColumn id="13" xr3:uid="{ACF3617F-A15C-4BA2-B462-292C6FA369C1}" name="Nome_file" dataDxfId="0" dataCellStyle="Collegamento ipertestuale"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -947,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.21875" customWidth="1"/>
@@ -956,7 +993,7 @@
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -996,16 +1033,20 @@
       <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1014,158 +1055,170 @@
         <v>1969</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
         <v>82</v>
       </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>1967</v>
+        <v>57</v>
+      </c>
+      <c r="E3" s="3">
+        <v>25064</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>1968</v>
+        <v>60</v>
+      </c>
+      <c r="E4" s="3">
+        <v>25081</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>1968</v>
+        <v>57</v>
+      </c>
+      <c r="E5" s="3">
+        <v>25479</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>1968</v>
+        <v>60</v>
+      </c>
+      <c r="E6" s="3">
+        <v>23511</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1174,10 +1227,10 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1186,50 +1239,51 @@
         <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="L7" t="s">
+        <v>13</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>1968</v>
+        <v>1992</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1238,7 +1292,7 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -1250,18 +1304,20 @@
         <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1270,7 +1326,7 @@
         <v>15</v>
       </c>
       <c r="E10">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -1282,18 +1338,20 @@
         <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1302,7 +1360,7 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -1314,24 +1372,26 @@
         <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>1968</v>
@@ -1346,24 +1406,26 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>1968</v>
@@ -1378,300 +1440,326 @@
         <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="3">
-        <v>25064</v>
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>1969</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="3">
-        <v>25081</v>
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>1969</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="3">
-        <v>25479</v>
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>1970</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" s="3">
-        <v>25485</v>
+        <v>46</v>
+      </c>
+      <c r="E18">
+        <v>1968</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="3">
-        <v>23511</v>
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>1968</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20">
+        <v>1967</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21">
+        <v>1968</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>47</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
         <v>15</v>
       </c>
-      <c r="E20">
-        <v>1969</v>
-      </c>
-      <c r="F20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21">
-        <v>1992</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" t="s">
-        <v>84</v>
-      </c>
-      <c r="K21" t="s">
-        <v>87</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="E22">
+        <v>1968</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>101</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="4">
-        <v>24746</v>
-      </c>
-      <c r="F22" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" t="s">
-        <v>114</v>
-      </c>
-      <c r="K22" t="s">
-        <v>113</v>
-      </c>
-      <c r="L22" t="s">
-        <v>144</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>141</v>
@@ -1680,7 +1768,7 @@
         <v>141</v>
       </c>
       <c r="E23" s="4">
-        <v>24777</v>
+        <v>24746</v>
       </c>
       <c r="F23" t="s">
         <v>151</v>
@@ -1698,15 +1786,17 @@
         <v>144</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>141</v>
@@ -1715,7 +1805,7 @@
         <v>141</v>
       </c>
       <c r="E24" s="4">
-        <v>24838</v>
+        <v>24777</v>
       </c>
       <c r="F24" t="s">
         <v>151</v>
@@ -1733,15 +1823,17 @@
         <v>144</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
         <v>141</v>
@@ -1750,7 +1842,7 @@
         <v>141</v>
       </c>
       <c r="E25" s="4">
-        <v>24869</v>
+        <v>24838</v>
       </c>
       <c r="F25" t="s">
         <v>151</v>
@@ -1768,15 +1860,17 @@
         <v>144</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -1785,7 +1879,7 @@
         <v>141</v>
       </c>
       <c r="E26" s="4">
-        <v>24898</v>
+        <v>24869</v>
       </c>
       <c r="F26" t="s">
         <v>151</v>
@@ -1803,15 +1897,17 @@
         <v>144</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="N26" s="5"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
@@ -1820,7 +1916,7 @@
         <v>141</v>
       </c>
       <c r="E27" s="4">
-        <v>24959</v>
+        <v>24898</v>
       </c>
       <c r="F27" t="s">
         <v>151</v>
@@ -1829,24 +1925,26 @@
         <v>142</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="K27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L27" t="s">
         <v>144</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="N27" s="5"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
         <v>141</v>
@@ -1855,7 +1953,7 @@
         <v>141</v>
       </c>
       <c r="E28" s="4">
-        <v>24990</v>
+        <v>24959</v>
       </c>
       <c r="F28" t="s">
         <v>151</v>
@@ -1873,15 +1971,17 @@
         <v>144</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="N28" s="5"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
         <v>141</v>
@@ -1890,7 +1990,7 @@
         <v>141</v>
       </c>
       <c r="E29" s="4">
-        <v>25082</v>
+        <v>24990</v>
       </c>
       <c r="F29" t="s">
         <v>151</v>
@@ -1899,7 +1999,7 @@
         <v>142</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="K29" t="s">
         <v>112</v>
@@ -1908,15 +2008,17 @@
         <v>144</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="N29" s="5"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>141</v>
@@ -1925,7 +2027,7 @@
         <v>141</v>
       </c>
       <c r="E30" s="4">
-        <v>25173</v>
+        <v>25082</v>
       </c>
       <c r="F30" t="s">
         <v>151</v>
@@ -1934,117 +2036,128 @@
         <v>142</v>
       </c>
       <c r="H30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L30" t="s">
         <v>144</v>
       </c>
       <c r="M30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N30" s="5"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="4">
+        <v>25173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" t="s">
+        <v>115</v>
+      </c>
+      <c r="K31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" t="s">
+        <v>144</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31">
-        <v>1968</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31" t="s">
-        <v>47</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N31" s="5"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32">
-        <v>1968</v>
+        <v>152</v>
+      </c>
+      <c r="E32" s="3">
+        <v>25485</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="K32" t="s">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>148</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N32" s="5"/>
+      <c r="O32" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
-    <hyperlink ref="M5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
-    <hyperlink ref="M6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
-    <hyperlink ref="M7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
-    <hyperlink ref="M8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
-    <hyperlink ref="M9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
-    <hyperlink ref="M10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
-    <hyperlink ref="M11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
-    <hyperlink ref="M4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
-    <hyperlink ref="M12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
-    <hyperlink ref="M13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
-    <hyperlink ref="M16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
-    <hyperlink ref="M18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
-    <hyperlink ref="M20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
-    <hyperlink ref="M27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
-    <hyperlink ref="M23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
-    <hyperlink ref="M30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
-    <hyperlink ref="M28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
-    <hyperlink ref="M29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
-    <hyperlink ref="M31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
-    <hyperlink ref="M24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
-    <hyperlink ref="M22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
-    <hyperlink ref="M21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
-    <hyperlink ref="M14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
-    <hyperlink ref="M25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
-    <hyperlink ref="M32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
-    <hyperlink ref="M15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
+    <hyperlink ref="M7" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
+    <hyperlink ref="M9" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
+    <hyperlink ref="M11" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
+    <hyperlink ref="M12" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
+    <hyperlink ref="M13" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
+    <hyperlink ref="M14" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
+    <hyperlink ref="M15" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
+    <hyperlink ref="M16" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
+    <hyperlink ref="M17" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
+    <hyperlink ref="M10" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
+    <hyperlink ref="M18" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
+    <hyperlink ref="M19" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
+    <hyperlink ref="M4" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
+    <hyperlink ref="M32" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
+    <hyperlink ref="M2" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
+    <hyperlink ref="M28" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
+    <hyperlink ref="M24" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
+    <hyperlink ref="M31" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
+    <hyperlink ref="M29" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
+    <hyperlink ref="M30" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
+    <hyperlink ref="M21" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
+    <hyperlink ref="M25" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
+    <hyperlink ref="M23" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
+    <hyperlink ref="M8" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
+    <hyperlink ref="M20" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
+    <hyperlink ref="M26" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
+    <hyperlink ref="M22" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
+    <hyperlink ref="M3" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
+    <hyperlink ref="M5" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
+    <hyperlink ref="M6" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBA4E05-3500-4A6C-AE15-B1C4B51ACED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7772B68-2A7C-4323-8C1D-07563A6E2C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -519,6 +519,30 @@
   </si>
   <si>
     <t>Delegazione, ministero degli esteri.jpg</t>
+  </si>
+  <si>
+    <t>Statuto di Stella Rossa - Fronte Rivoluzionario Marxista-Leninista</t>
+  </si>
+  <si>
+    <t>Stella Rossa - Fronte Rivoluzionario Marxista-Leninista</t>
+  </si>
+  <si>
+    <t>AMI-0032</t>
+  </si>
+  <si>
+    <t>Testo</t>
+  </si>
+  <si>
+    <t>Galassia m-l</t>
+  </si>
+  <si>
+    <t>Vincenzo Calò</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/statuto-stella-rossa</t>
+  </si>
+  <si>
+    <t>STATUTO DI STELLA ROSSA.txt</t>
   </si>
 </sst>
 </file>
@@ -642,10 +666,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:N32" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:N32" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N32">
-    <sortCondition ref="F1:F32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:N51" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:N51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N51">
+    <sortCondition ref="A1:A51"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{2154B3EB-64E4-4E6D-8A0C-04D65D066E62}" name="ID"/>
@@ -984,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.21875" customWidth="1"/>
@@ -1040,13 +1064,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1055,170 +1079,168 @@
         <v>1969</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
         <v>82</v>
       </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
       <c r="M2" s="1" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="3">
-        <v>25064</v>
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>1967</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="3">
-        <v>25081</v>
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>1968</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>157</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N4" s="5"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="3">
-        <v>25479</v>
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>1968</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>158</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N5" s="5"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3">
-        <v>23511</v>
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>1968</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>159</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N6" s="5"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1227,10 +1249,10 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1239,51 +1261,54 @@
         <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>1992</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1292,7 +1317,7 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -1304,20 +1329,20 @@
         <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1326,7 +1351,7 @@
         <v>15</v>
       </c>
       <c r="E10">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -1338,20 +1363,20 @@
         <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1360,7 +1385,7 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -1372,26 +1397,26 @@
         <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E12">
         <v>1968</v>
@@ -1406,26 +1431,26 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>1968</v>
@@ -1440,326 +1465,328 @@
         <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E14">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15">
-        <v>1969</v>
+        <v>57</v>
+      </c>
+      <c r="E15" s="3">
+        <v>25064</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N15" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16">
-        <v>1969</v>
+        <v>60</v>
+      </c>
+      <c r="E16" s="3">
+        <v>25081</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N16" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>1970</v>
+        <v>57</v>
+      </c>
+      <c r="E17" s="3">
+        <v>25479</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N17" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18">
-        <v>1968</v>
+        <v>152</v>
+      </c>
+      <c r="E18" s="3">
+        <v>25485</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="K18" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19">
-        <v>1968</v>
+        <v>60</v>
+      </c>
+      <c r="E19" s="3">
+        <v>23511</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="K19" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N19" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="K20" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E21">
-        <v>1968</v>
+        <v>1992</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22">
-        <v>1968</v>
+        <v>141</v>
+      </c>
+      <c r="E22" s="4">
+        <v>24746</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="K22" t="s">
-        <v>146</v>
+        <v>113</v>
+      </c>
+      <c r="L22" t="s">
+        <v>144</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>141</v>
@@ -1768,7 +1795,7 @@
         <v>141</v>
       </c>
       <c r="E23" s="4">
-        <v>24746</v>
+        <v>24777</v>
       </c>
       <c r="F23" t="s">
         <v>151</v>
@@ -1786,17 +1813,17 @@
         <v>144</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
         <v>141</v>
@@ -1805,7 +1832,7 @@
         <v>141</v>
       </c>
       <c r="E24" s="4">
-        <v>24777</v>
+        <v>24838</v>
       </c>
       <c r="F24" t="s">
         <v>151</v>
@@ -1823,17 +1850,17 @@
         <v>144</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
         <v>141</v>
@@ -1842,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="E25" s="4">
-        <v>24838</v>
+        <v>24869</v>
       </c>
       <c r="F25" t="s">
         <v>151</v>
@@ -1860,17 +1887,17 @@
         <v>144</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -1879,7 +1906,7 @@
         <v>141</v>
       </c>
       <c r="E26" s="4">
-        <v>24869</v>
+        <v>24898</v>
       </c>
       <c r="F26" t="s">
         <v>151</v>
@@ -1897,17 +1924,17 @@
         <v>144</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>141</v>
@@ -1916,7 +1943,7 @@
         <v>141</v>
       </c>
       <c r="E27" s="4">
-        <v>24898</v>
+        <v>24959</v>
       </c>
       <c r="F27" t="s">
         <v>151</v>
@@ -1925,26 +1952,26 @@
         <v>142</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L27" t="s">
         <v>144</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
         <v>141</v>
@@ -1953,7 +1980,7 @@
         <v>141</v>
       </c>
       <c r="E28" s="4">
-        <v>24959</v>
+        <v>24990</v>
       </c>
       <c r="F28" t="s">
         <v>151</v>
@@ -1971,17 +1998,17 @@
         <v>144</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>141</v>
@@ -1990,7 +2017,7 @@
         <v>141</v>
       </c>
       <c r="E29" s="4">
-        <v>24990</v>
+        <v>25082</v>
       </c>
       <c r="F29" t="s">
         <v>151</v>
@@ -1999,7 +2026,7 @@
         <v>142</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="K29" t="s">
         <v>112</v>
@@ -2008,17 +2035,17 @@
         <v>144</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>141</v>
@@ -2027,7 +2054,7 @@
         <v>141</v>
       </c>
       <c r="E30" s="4">
-        <v>25082</v>
+        <v>25173</v>
       </c>
       <c r="F30" t="s">
         <v>151</v>
@@ -2036,124 +2063,228 @@
         <v>142</v>
       </c>
       <c r="H30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s">
         <v>144</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="4">
-        <v>25173</v>
+        <v>98</v>
+      </c>
+      <c r="E31">
+        <v>1968</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="H31" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>111</v>
-      </c>
-      <c r="L31" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" s="3">
-        <v>25485</v>
+        <v>15</v>
+      </c>
+      <c r="E32">
+        <v>1968</v>
       </c>
       <c r="F32" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H32" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" t="s">
+        <v>161</v>
+      </c>
+      <c r="E33">
+        <v>1970</v>
+      </c>
+      <c r="F33" t="s">
+        <v>163</v>
+      </c>
+      <c r="H33" t="s">
+        <v>164</v>
+      </c>
+      <c r="I33" t="s">
+        <v>165</v>
+      </c>
+      <c r="K33" t="s">
+        <v>113</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M34" s="1"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M35" s="1"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M36" s="1"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M37" s="1"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M38" s="1"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M39" s="1"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M40" s="1"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M41" s="1"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M42" s="1"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M43" s="1"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M44" s="1"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M45" s="1"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M46" s="1"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M47" s="1"/>
+      <c r="N47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M48" s="1"/>
+      <c r="N48" s="5"/>
+    </row>
+    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M49" s="1"/>
+      <c r="N49" s="5"/>
+    </row>
+    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M50" s="1"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M51" s="1"/>
+      <c r="N51" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M7" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
-    <hyperlink ref="M9" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
-    <hyperlink ref="M11" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
-    <hyperlink ref="M12" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
-    <hyperlink ref="M13" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
-    <hyperlink ref="M14" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
-    <hyperlink ref="M15" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
-    <hyperlink ref="M16" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
-    <hyperlink ref="M17" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
-    <hyperlink ref="M10" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
-    <hyperlink ref="M18" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
-    <hyperlink ref="M19" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
-    <hyperlink ref="M4" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
-    <hyperlink ref="M32" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
-    <hyperlink ref="M2" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
-    <hyperlink ref="M28" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
-    <hyperlink ref="M24" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
-    <hyperlink ref="M31" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
-    <hyperlink ref="M29" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
-    <hyperlink ref="M30" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
-    <hyperlink ref="M21" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
-    <hyperlink ref="M25" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
-    <hyperlink ref="M23" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
-    <hyperlink ref="M8" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
-    <hyperlink ref="M20" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
-    <hyperlink ref="M26" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
-    <hyperlink ref="M22" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
-    <hyperlink ref="M3" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
-    <hyperlink ref="M5" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
-    <hyperlink ref="M6" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
+    <hyperlink ref="M5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
+    <hyperlink ref="M6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
+    <hyperlink ref="M7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
+    <hyperlink ref="M8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
+    <hyperlink ref="M9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
+    <hyperlink ref="M10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
+    <hyperlink ref="M11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
+    <hyperlink ref="M4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
+    <hyperlink ref="M12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
+    <hyperlink ref="M13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
+    <hyperlink ref="M16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
+    <hyperlink ref="M18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
+    <hyperlink ref="M20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
+    <hyperlink ref="M27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
+    <hyperlink ref="M23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
+    <hyperlink ref="M30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
+    <hyperlink ref="M28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
+    <hyperlink ref="M29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
+    <hyperlink ref="M31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
+    <hyperlink ref="M24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
+    <hyperlink ref="M22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
+    <hyperlink ref="M21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
+    <hyperlink ref="M14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
+    <hyperlink ref="M25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
+    <hyperlink ref="M32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
+    <hyperlink ref="M15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
+    <hyperlink ref="M17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
+    <hyperlink ref="M19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7772B68-2A7C-4323-8C1D-07563A6E2C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE665D5-DDC8-4B30-8E74-2CBCF9CB7017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="172">
   <si>
     <t>ID</t>
   </si>
@@ -543,6 +543,18 @@
   </si>
   <si>
     <t>STATUTO DI STELLA ROSSA.txt</t>
+  </si>
+  <si>
+    <t>Fosco Dinucci; Osvaldo Pesce</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce; Mao Zedong</t>
+  </si>
+  <si>
+    <t>Fosco Dinucci; Mao Zedong; Lin Biao; Zhou Enlai; Kang Sheng; Chen Boda</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce; Dino Dini; Mao Zedong; Zhou Enlai; Jiang Qing; Kang Sheng; Chen Boda; Yao Wenyuan</t>
   </si>
 </sst>
 </file>
@@ -1011,10 +1023,13 @@
   <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="53.5546875" customWidth="1"/>
+    <col min="3" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="13" max="13" width="101.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1498,6 +1513,9 @@
       <c r="H14" t="s">
         <v>51</v>
       </c>
+      <c r="I14" t="s">
+        <v>168</v>
+      </c>
       <c r="K14" t="s">
         <v>54</v>
       </c>
@@ -1532,6 +1550,9 @@
       <c r="H15" t="s">
         <v>51</v>
       </c>
+      <c r="I15" t="s">
+        <v>171</v>
+      </c>
       <c r="K15" t="s">
         <v>58</v>
       </c>
@@ -1568,6 +1589,9 @@
       <c r="H16" t="s">
         <v>51</v>
       </c>
+      <c r="I16" t="s">
+        <v>169</v>
+      </c>
       <c r="K16" t="s">
         <v>58</v>
       </c>
@@ -1603,6 +1627,9 @@
       </c>
       <c r="H17" t="s">
         <v>51</v>
+      </c>
+      <c r="I17" t="s">
+        <v>170</v>
       </c>
       <c r="K17" t="s">
         <v>58</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE665D5-DDC8-4B30-8E74-2CBCF9CB7017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2449FC33-BC6C-41EB-BF23-37E5FA668DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="181">
   <si>
     <t>ID</t>
   </si>
@@ -555,6 +555,33 @@
   </si>
   <si>
     <t>Osvaldo Pesce; Dino Dini; Mao Zedong; Zhou Enlai; Jiang Qing; Kang Sheng; Chen Boda; Yao Wenyuan</t>
+  </si>
+  <si>
+    <t>AMI-0033</t>
+  </si>
+  <si>
+    <t>Verbale della conversazione del Presidente Mao con la delegazione comunista (marxista-leninista) italiana</t>
+  </si>
+  <si>
+    <t>Testo_bilingue</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce; Dino Dini; Mao Zedong</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/conversazione-mao-pesce</t>
+  </si>
+  <si>
+    <t>Nome_file_originale</t>
+  </si>
+  <si>
+    <t>mao-pesce-italiano.txt</t>
+  </si>
+  <si>
+    <t>mao-pesce-cinese.txt</t>
+  </si>
+  <si>
+    <t>Nome_file_traduzione</t>
   </si>
 </sst>
 </file>
@@ -678,12 +705,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:N51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:N51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:P51" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:P51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N51">
     <sortCondition ref="A1:A51"/>
   </sortState>
-  <tableColumns count="14">
+  <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{2154B3EB-64E4-4E6D-8A0C-04D65D066E62}" name="ID"/>
     <tableColumn id="2" xr3:uid="{7C80280B-722C-4CED-A5F4-3F72F39F1DFC}" name="Titolo"/>
     <tableColumn id="3" xr3:uid="{42E23130-656A-4022-81E0-AF9117BAC245}" name="Organizzazione"/>
@@ -698,6 +725,8 @@
     <tableColumn id="10" xr3:uid="{AEDEDEC1-9395-48B6-A4EF-01A581661641}" name="Note"/>
     <tableColumn id="11" xr3:uid="{575D6553-9BD2-40E4-8055-A706418FDCC7}" name="URL" dataCellStyle="Collegamento ipertestuale"/>
     <tableColumn id="13" xr3:uid="{ACF3617F-A15C-4BA2-B462-292C6FA369C1}" name="Nome_file" dataDxfId="0" dataCellStyle="Collegamento ipertestuale"/>
+    <tableColumn id="16" xr3:uid="{0BDE9F47-E369-4064-B628-A58828AF6D96}" name="Nome_file_originale"/>
+    <tableColumn id="17" xr3:uid="{745EB64B-EB38-4333-A624-A421897E58C7}" name="Nome_file_traduzione"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1020,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
@@ -1030,9 +1059,10 @@
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="101.33203125" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1075,9 +1105,14 @@
       <c r="N1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1149,7 @@
       <c r="N2" s="5"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1148,7 +1183,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1182,7 +1217,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1216,7 +1251,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1250,7 +1285,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1284,7 +1319,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1318,7 +1353,7 @@
       <c r="N8" s="5"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1352,7 +1387,7 @@
       <c r="N9" s="5"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1386,7 +1421,7 @@
       <c r="N10" s="5"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1420,7 +1455,7 @@
       <c r="N11" s="5"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1454,7 +1489,7 @@
       <c r="N12" s="5"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1488,7 +1523,7 @@
       <c r="N13" s="5"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1525,7 +1560,7 @@
       <c r="N14" s="5"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1564,7 +1599,7 @@
       </c>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -2172,7 +2207,7 @@
       <c r="N32" s="5"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>162</v>
       </c>
@@ -2207,63 +2242,95 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M34" s="1"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="3">
+        <v>25063</v>
+      </c>
+      <c r="F34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
+        <v>175</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="N34" s="5"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" t="s">
+        <v>179</v>
+      </c>
+      <c r="P34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M35" s="1"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M36" s="1"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M37" s="1"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M38" s="1"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M39" s="1"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M40" s="1"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M41" s="1"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M42" s="1"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M43" s="1"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M44" s="1"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M45" s="1"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M46" s="1"/>
       <c r="N46" s="5"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M47" s="1"/>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M48" s="1"/>
       <c r="N48" s="5"/>
     </row>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2449FC33-BC6C-41EB-BF23-37E5FA668DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD1D3F-AE5C-4D08-8D41-F40790248705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="188">
   <si>
     <t>ID</t>
   </si>
@@ -582,6 +582,27 @@
   </si>
   <si>
     <t>Nome_file_traduzione</t>
+  </si>
+  <si>
+    <t>AMI-0034</t>
+  </si>
+  <si>
+    <t>Istruzioni del Presidente Mao sulla relazione di Kang Sheng riguardante la raccolta di materiale sulle elezioni parlamentari nei paesi capitalisti</t>
+  </si>
+  <si>
+    <t>Partito Comunista Cinese</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce; Mao Zedong; Dino Dini</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/istruzioni-mao-italiano</t>
+  </si>
+  <si>
+    <t>istruzioni-mao-cinese.txt</t>
+  </si>
+  <si>
+    <t>istruzioni-mao-italiano.txt</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1075,7 @@
   <cols>
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
     <col min="3" max="4" width="20.77734375" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
@@ -2279,8 +2300,43 @@
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M35" s="1"/>
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="3">
+        <v>25081</v>
+      </c>
+      <c r="F35" t="s">
+        <v>174</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" t="s">
+        <v>184</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="N35" s="5"/>
+      <c r="O35" t="s">
+        <v>186</v>
+      </c>
+      <c r="P35" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M36" s="1"/>
@@ -2379,10 +2435,11 @@
     <hyperlink ref="M15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
     <hyperlink ref="M17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
     <hyperlink ref="M19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
+    <hyperlink ref="M35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId31"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD1D3F-AE5C-4D08-8D41-F40790248705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6096DB55-418D-46E3-AC05-56E0ED38E1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="3444" yWindow="2772" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="188">
   <si>
     <t>ID</t>
   </si>
@@ -2327,6 +2327,9 @@
       <c r="I35" t="s">
         <v>184</v>
       </c>
+      <c r="J35" t="s">
+        <v>51</v>
+      </c>
       <c r="M35" s="1" t="s">
         <v>185</v>
       </c>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6096DB55-418D-46E3-AC05-56E0ED38E1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD85DD4-31A8-4F99-908B-E417BBDCF6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3444" yWindow="2772" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD85DD4-31A8-4F99-908B-E417BBDCF6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B68E5F-21AA-4FB1-A3EC-1F4114447F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="190">
   <si>
     <t>ID</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Catania</t>
   </si>
   <si>
-    <t>UCI (m-l) - Servire il Popolo</t>
-  </si>
-  <si>
     <t>Unione dei Comunisti Italiani (marxisti-leninisti); Servire il Popolo; Volantino</t>
   </si>
   <si>
@@ -386,12 +383,6 @@
     <t>Lavoro Politico</t>
   </si>
   <si>
-    <t>Lavoro Politico; Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
-  </si>
-  <si>
-    <t>Lavoro Politico; Partito Comunista d'Italia (marxista-leninista)</t>
-  </si>
-  <si>
     <t>https://archive.org/details/lavoro-politico-04/mode/2up</t>
   </si>
   <si>
@@ -470,9 +461,6 @@
     <t>Verona</t>
   </si>
   <si>
-    <t>Lavoro Politico;  Partito Comunista d'Italia (marxista-leninista)</t>
-  </si>
-  <si>
     <t>Proveniente dall'Archivio Storico della Nuova Sinistra "Marco Pezzi"</t>
   </si>
   <si>
@@ -533,9 +521,6 @@
     <t>Testo</t>
   </si>
   <si>
-    <t>Galassia m-l</t>
-  </si>
-  <si>
     <t>Vincenzo Calò</t>
   </si>
   <si>
@@ -587,9 +572,6 @@
     <t>AMI-0034</t>
   </si>
   <si>
-    <t>Istruzioni del Presidente Mao sulla relazione di Kang Sheng riguardante la raccolta di materiale sulle elezioni parlamentari nei paesi capitalisti</t>
-  </si>
-  <si>
     <t>Partito Comunista Cinese</t>
   </si>
   <si>
@@ -603,6 +585,30 @@
   </si>
   <si>
     <t>istruzioni-mao-italiano.txt</t>
+  </si>
+  <si>
+    <t>AMI-0035</t>
+  </si>
+  <si>
+    <t>Viva il popolo cinese</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
+    <t>Partito Comunista d'Italia (marxista-leninista); Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/viva-il-popolo-cinese/mode/2up</t>
+  </si>
+  <si>
+    <t>Riviste marxiste-leniniste</t>
+  </si>
+  <si>
+    <t>Galassia marxista-leninista</t>
+  </si>
+  <si>
+    <t>Nota del Presidente Mao sulla relazione di Kang Sheng riguardante la raccolta di materiale sulle elezioni parlamentari nei paesi capitalisti</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1082,9 @@
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
     <col min="3" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="101.33203125" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
@@ -1109,10 +1116,10 @@
         <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>16</v>
@@ -1124,13 +1131,13 @@
         <v>7</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1159,13 +1166,13 @@
         <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="2"/>
@@ -1199,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
@@ -1233,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="2"/>
@@ -1267,7 +1274,7 @@
         <v>24</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="2"/>
@@ -1335,7 +1342,7 @@
         <v>30</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="2"/>
@@ -1369,7 +1376,7 @@
         <v>30</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="2"/>
@@ -1403,7 +1410,7 @@
         <v>30</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="2"/>
@@ -1437,7 +1444,7 @@
         <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="2"/>
@@ -1471,7 +1478,7 @@
         <v>30</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="2"/>
@@ -1505,7 +1512,7 @@
         <v>47</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="2"/>
@@ -1539,14 +1546,14 @@
         <v>47</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
@@ -1567,23 +1574,23 @@
         <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I14" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K14" t="s">
         <v>54</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1604,25 +1611,25 @@
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K15" t="s">
         <v>58</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1643,10 +1650,10 @@
         <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="K16" t="s">
         <v>58</v>
@@ -1655,13 +1662,13 @@
         <v>61</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
@@ -1682,10 +1689,10 @@
         <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I17" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K17" t="s">
         <v>58</v>
@@ -1694,13 +1701,13 @@
         <v>63</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1709,38 +1716,38 @@
         <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E18" s="3">
         <v>25485</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G18" t="s">
         <v>66</v>
       </c>
       <c r="H18" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" t="s">
         <v>67</v>
       </c>
-      <c r="K18" t="s">
-        <v>68</v>
-      </c>
       <c r="M18" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
         <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
       </c>
       <c r="D19" t="s">
         <v>60</v>
@@ -1755,28 +1762,28 @@
         <v>11</v>
       </c>
       <c r="H19" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" t="s">
         <v>70</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="N19" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -1785,29 +1792,29 @@
         <v>1969</v>
       </c>
       <c r="F20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
         <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
       </c>
       <c r="E21">
         <v>1992</v>
@@ -1816,362 +1823,365 @@
         <v>10</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E22" s="4">
         <v>24746</v>
       </c>
       <c r="F22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="K22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E23" s="4">
         <v>24777</v>
       </c>
       <c r="F23" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="K23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L23" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E24" s="4">
         <v>24838</v>
       </c>
       <c r="F24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H24" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="K24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E25" s="4">
         <v>24869</v>
       </c>
       <c r="F25" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G25" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H25" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" t="s">
+        <v>112</v>
+      </c>
+      <c r="L25" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="K25" t="s">
-        <v>113</v>
-      </c>
-      <c r="L25" t="s">
-        <v>144</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E26" s="4">
         <v>24898</v>
       </c>
       <c r="F26" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="K26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L26" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E27" s="4">
         <v>24959</v>
       </c>
       <c r="F27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="K27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E28" s="4">
         <v>24990</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="K28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E29" s="4">
         <v>25082</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G29" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="K29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E30" s="4">
         <v>25173</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G30" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H30" t="s">
-        <v>115</v>
+        <v>187</v>
+      </c>
+      <c r="J30" t="s">
+        <v>185</v>
       </c>
       <c r="K30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31">
         <v>1968</v>
@@ -2189,17 +2199,17 @@
         <v>47</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2220,55 +2230,52 @@
         <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
-      </c>
-      <c r="D33" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E33">
         <v>1970</v>
       </c>
       <c r="F33" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H33" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="I33" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
         <v>51</v>
@@ -2277,37 +2284,40 @@
         <v>25063</v>
       </c>
       <c r="F34" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>170</v>
+      </c>
+      <c r="J34" t="s">
+        <v>177</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2316,33 +2326,56 @@
         <v>25081</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J35" t="s">
         <v>51</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" t="s">
+        <v>180</v>
+      </c>
+      <c r="P35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="4">
+        <v>25416</v>
+      </c>
+      <c r="F36" t="s">
+        <v>147</v>
+      </c>
+      <c r="G36" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" t="s">
+        <v>188</v>
+      </c>
+      <c r="M36" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="P35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M36" s="1"/>
       <c r="N36" s="5"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
@@ -2439,10 +2472,11 @@
     <hyperlink ref="M17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
     <hyperlink ref="M19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
     <hyperlink ref="M35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
+    <hyperlink ref="M36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId32"/>
+    <tablePart r:id="rId33"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B68E5F-21AA-4FB1-A3EC-1F4114447F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0B0D4C-5211-4C1A-96E2-888C5167E0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="195">
   <si>
     <t>ID</t>
   </si>
@@ -609,6 +609,21 @@
   </si>
   <si>
     <t>Nota del Presidente Mao sulla relazione di Kang Sheng riguardante la raccolta di materiale sulle elezioni parlamentari nei paesi capitalisti</t>
+  </si>
+  <si>
+    <t>AMI-0036</t>
+  </si>
+  <si>
+    <t>Savelli</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/in-caso-di-golpe/mode/2up</t>
+  </si>
+  <si>
+    <t>In caso di golpe: Manuale teorico-pratico per il cittadino, di resistenza totale e di guerra di popolo, di guerriglia e di controguerriglia</t>
   </si>
 </sst>
 </file>
@@ -2379,7 +2394,36 @@
       <c r="N36" s="5"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M37" s="1"/>
+      <c r="A37" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37">
+        <v>1975</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>192</v>
+      </c>
+      <c r="H37" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" t="s">
+        <v>157</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="N37" s="5"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
@@ -2475,8 +2519,9 @@
     <hyperlink ref="M36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId33"/>
   <tableParts count="1">
-    <tablePart r:id="rId33"/>
+    <tablePart r:id="rId34"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0B0D4C-5211-4C1A-96E2-888C5167E0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04C9BB0-DB87-4591-A474-B795FCF5B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="199">
   <si>
     <t>ID</t>
   </si>
@@ -624,6 +624,18 @@
   </si>
   <si>
     <t>In caso di golpe: Manuale teorico-pratico per il cittadino, di resistenza totale e di guerra di popolo, di guerriglia e di controguerriglia</t>
+  </si>
+  <si>
+    <t>Editore</t>
+  </si>
+  <si>
+    <t>Periodici Operai</t>
+  </si>
+  <si>
+    <t>Synergon</t>
+  </si>
+  <si>
+    <t>Bologna</t>
   </si>
 </sst>
 </file>
@@ -747,16 +759,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:P51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:P51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:Q51" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:Q51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O51">
     <sortCondition ref="A1:A51"/>
   </sortState>
-  <tableColumns count="16">
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{2154B3EB-64E4-4E6D-8A0C-04D65D066E62}" name="ID"/>
     <tableColumn id="2" xr3:uid="{7C80280B-722C-4CED-A5F4-3F72F39F1DFC}" name="Titolo"/>
     <tableColumn id="3" xr3:uid="{42E23130-656A-4022-81E0-AF9117BAC245}" name="Organizzazione"/>
     <tableColumn id="4" xr3:uid="{2C4058CC-38DB-4956-9E67-D3EA7FC7C935}" name="Autore"/>
+    <tableColumn id="15" xr3:uid="{0B0E529D-59E2-49D0-8832-81A3991ABB7A}" name="Editore"/>
     <tableColumn id="5" xr3:uid="{298026F6-C95C-4BE5-939D-B82BDF27858C}" name="Data"/>
     <tableColumn id="6" xr3:uid="{C5B41BAF-F262-46B8-B4E1-9009830092DD}" name="Tipo"/>
     <tableColumn id="7" xr3:uid="{4B20EDD1-B200-43AC-BE45-669E891C9C85}" name="Luogo"/>
@@ -1091,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
@@ -1105,7 +1118,7 @@
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1119,43 +1132,46 @@
         <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1168,31 +1184,34 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
         <v>1969</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>81</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O2" s="5"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1205,28 +1224,31 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
         <v>1967</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O3" s="5"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1239,28 +1261,31 @@
       <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
         <v>1968</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O4" s="5"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1273,28 +1298,31 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
         <v>1968</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>18</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O5" s="5"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1307,28 +1335,31 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
         <v>1968</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>11</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O6" s="5"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1341,28 +1372,31 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
         <v>1968</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>18</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O7" s="5"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1375,28 +1409,31 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
         <v>1968</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>18</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O8" s="5"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1409,28 +1446,31 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
         <v>1969</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>18</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>30</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O9" s="5"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1443,28 +1483,31 @@
       <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
         <v>1969</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>11</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>18</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O10" s="5"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1477,28 +1520,31 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
         <v>1970</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>18</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O11" s="5"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1511,28 +1557,31 @@
       <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
         <v>1968</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>11</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>18</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O12" s="5"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1545,28 +1594,31 @@
       <c r="D13" t="s">
         <v>49</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
         <v>1968</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>20</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>11</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>18</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>47</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O13" s="5"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1579,31 +1631,34 @@
       <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14">
         <v>1967</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>53</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>188</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>163</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O14" s="5"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -1616,33 +1671,33 @@
       <c r="D15" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25064</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>55</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>11</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>188</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>166</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="O15" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -1655,33 +1710,33 @@
       <c r="D16" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>25081</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>55</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>11</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>188</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>164</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="O16" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -1694,33 +1749,33 @@
       <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25479</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>55</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>11</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>188</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>165</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="O17" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -1733,28 +1788,28 @@
       <c r="D18" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25485</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>146</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>66</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>188</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O18" s="5"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -1767,30 +1822,30 @@
       <c r="D19" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>23511</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>55</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>11</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>188</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>70</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N19" s="5" t="s">
+      <c r="O19" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -1803,25 +1858,25 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>1969</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>79</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>83</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>81</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O20" s="5"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -1831,25 +1886,31 @@
       <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="E21">
-        <v>1992</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21">
+        <v>1993</v>
+      </c>
+      <c r="G21" t="s">
         <v>10</v>
       </c>
       <c r="H21" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" t="s">
         <v>83</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>86</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O21" s="5"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -1862,31 +1923,31 @@
       <c r="D22" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" s="4">
         <v>24746</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>147</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>139</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>187</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>112</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>140</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O22" s="5"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -1899,31 +1960,31 @@
       <c r="D23" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <v>24777</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>147</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>139</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>187</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>112</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>140</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O23" s="5"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>102</v>
       </c>
@@ -1936,31 +1997,31 @@
       <c r="D24" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <v>24838</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>147</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>139</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>187</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>112</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>140</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O24" s="5"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -1973,31 +2034,31 @@
       <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" s="4">
         <v>24869</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>147</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>139</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>187</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>112</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>140</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N25" s="5"/>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O25" s="5"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -2010,31 +2071,31 @@
       <c r="D26" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <v>24898</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>147</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>139</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>187</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>112</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>140</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O26" s="5"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>105</v>
       </c>
@@ -2047,31 +2108,31 @@
       <c r="D27" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" s="4">
         <v>24959</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>147</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>139</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>187</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>111</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>140</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N27" s="5"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O27" s="5"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>106</v>
       </c>
@@ -2084,31 +2145,31 @@
       <c r="D28" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" s="4">
         <v>24990</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>147</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>139</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>187</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>111</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>140</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N28" s="5"/>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O28" s="5"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>107</v>
       </c>
@@ -2121,31 +2182,31 @@
       <c r="D29" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <v>25082</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>147</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>139</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>187</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>111</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>140</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O29" s="5"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -2158,34 +2219,34 @@
       <c r="D30" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="4">
+      <c r="F30" s="4">
         <v>25173</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>147</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>139</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>187</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>185</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>110</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>140</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N30" s="5"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O30" s="5"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>109</v>
       </c>
@@ -2198,28 +2259,31 @@
       <c r="D31" t="s">
         <v>97</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
         <v>1968</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>20</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>11</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>18</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>47</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="N31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="N31" s="5"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O31" s="5"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -2232,28 +2296,31 @@
       <c r="D32" t="s">
         <v>15</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
         <v>1968</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>20</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>11</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>18</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>142</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O32" s="5"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>158</v>
       </c>
@@ -2263,29 +2330,29 @@
       <c r="C33" t="s">
         <v>157</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>1970</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>159</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>188</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>160</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>112</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="N33" s="5" t="s">
+      <c r="O33" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -2295,36 +2362,36 @@
       <c r="C34" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="3">
+      <c r="F34" s="3">
         <v>25063</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>169</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>11</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>188</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>170</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>177</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="N34" s="5"/>
-      <c r="O34" t="s">
+      <c r="O34" s="5"/>
+      <c r="P34" t="s">
         <v>174</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>176</v>
       </c>
@@ -2337,36 +2404,36 @@
       <c r="D35" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25081</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>169</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>11</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>188</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>178</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>51</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="N35" s="5"/>
-      <c r="O35" t="s">
+      <c r="O35" s="5"/>
+      <c r="P35" t="s">
         <v>180</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>182</v>
       </c>
@@ -2376,24 +2443,24 @@
       <c r="C36" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="4">
+      <c r="F36" s="4">
         <v>25416</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>147</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>184</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>188</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="N36" s="5"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>190</v>
       </c>
@@ -2401,122 +2468,125 @@
         <v>194</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
         <v>160</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37">
         <v>1975</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>10</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>192</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>83</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>157</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="N37" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N37" s="5"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M38" s="1"/>
-      <c r="N38" s="5"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M39" s="1"/>
-      <c r="N39" s="5"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M40" s="1"/>
-      <c r="N40" s="5"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M41" s="1"/>
-      <c r="N41" s="5"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M42" s="1"/>
-      <c r="N42" s="5"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M43" s="1"/>
-      <c r="N43" s="5"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M44" s="1"/>
-      <c r="N44" s="5"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M45" s="1"/>
-      <c r="N45" s="5"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M46" s="1"/>
-      <c r="N46" s="5"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M47" s="1"/>
-      <c r="N47" s="5"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M48" s="1"/>
-      <c r="N48" s="5"/>
-    </row>
-    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M49" s="1"/>
-      <c r="N49" s="5"/>
-    </row>
-    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M50" s="1"/>
-      <c r="N50" s="5"/>
-    </row>
-    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M51" s="1"/>
-      <c r="N51" s="5"/>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N38" s="1"/>
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N39" s="1"/>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N40" s="1"/>
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N41" s="1"/>
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N42" s="1"/>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N43" s="1"/>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N44" s="1"/>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N45" s="1"/>
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N46" s="1"/>
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N47" s="1"/>
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N48" s="1"/>
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N49" s="1"/>
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N50" s="1"/>
+      <c r="O50" s="5"/>
+    </row>
+    <row r="51" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N51" s="1"/>
+      <c r="O51" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
-    <hyperlink ref="M5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
-    <hyperlink ref="M6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
-    <hyperlink ref="M7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
-    <hyperlink ref="M8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
-    <hyperlink ref="M9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
-    <hyperlink ref="M10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
-    <hyperlink ref="M11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
-    <hyperlink ref="M4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
-    <hyperlink ref="M12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
-    <hyperlink ref="M13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
-    <hyperlink ref="M16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
-    <hyperlink ref="M18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
-    <hyperlink ref="M20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
-    <hyperlink ref="M27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
-    <hyperlink ref="M23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
-    <hyperlink ref="M30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
-    <hyperlink ref="M28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
-    <hyperlink ref="M29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
-    <hyperlink ref="M31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
-    <hyperlink ref="M24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
-    <hyperlink ref="M22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
-    <hyperlink ref="M21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
-    <hyperlink ref="M14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
-    <hyperlink ref="M25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
-    <hyperlink ref="M32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
-    <hyperlink ref="M15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
-    <hyperlink ref="M17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
-    <hyperlink ref="M19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
-    <hyperlink ref="M35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
-    <hyperlink ref="M36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
+    <hyperlink ref="N5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
+    <hyperlink ref="N6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
+    <hyperlink ref="N7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
+    <hyperlink ref="N8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
+    <hyperlink ref="N9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
+    <hyperlink ref="N10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
+    <hyperlink ref="N11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
+    <hyperlink ref="N4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
+    <hyperlink ref="N16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
+    <hyperlink ref="N18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
+    <hyperlink ref="N20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
+    <hyperlink ref="N27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
+    <hyperlink ref="N23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
+    <hyperlink ref="N30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
+    <hyperlink ref="N28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
+    <hyperlink ref="N29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
+    <hyperlink ref="N31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
+    <hyperlink ref="N24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
+    <hyperlink ref="N22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
+    <hyperlink ref="N21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
+    <hyperlink ref="N14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
+    <hyperlink ref="N25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
+    <hyperlink ref="N32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
+    <hyperlink ref="N15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
+    <hyperlink ref="N17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
+    <hyperlink ref="N19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
+    <hyperlink ref="N35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
+    <hyperlink ref="N36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId33"/>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04C9BB0-DB87-4591-A474-B795FCF5B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF4837D-E236-4BD1-966F-109BEFBDAB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="180">
   <si>
     <t>ID</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Luogo</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>URL</t>
   </si>
   <si>
@@ -80,18 +77,12 @@
     <t>Casa editrice in lingue estere</t>
   </si>
   <si>
-    <t>Edizione tascabile</t>
-  </si>
-  <si>
     <t>Autore</t>
   </si>
   <si>
     <t>Mao Zedong</t>
   </si>
   <si>
-    <t>Keywords</t>
-  </si>
-  <si>
     <t>Serie</t>
   </si>
   <si>
@@ -104,24 +95,15 @@
     <t>Opuscolo</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Maoismo; Teoria politica</t>
-  </si>
-  <si>
     <t>AMI-0002</t>
   </si>
   <si>
     <t>Dichiarazione del compagno Mao Tse-tung, presidente del Comitato Centrale del Partito Comunista Cinese, in appoggio alla lotta degli afroamericani contro la repressione violenta</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Maoismo; Internazionalismo</t>
-  </si>
-  <si>
     <t>Da dove provengono le idee giuste?</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Maoismo; Teoria politica; Filosofia</t>
-  </si>
-  <si>
     <t>https://archive.org/details/idee-giuste/mode/2up</t>
   </si>
   <si>
@@ -131,9 +113,6 @@
     <t>Preoccuparsi delle condizioni di vita delle masse fare attenzione ai metodi di lavoro</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Maoismo</t>
-  </si>
-  <si>
     <t>Sul rafforzamento del sistema dei comitati di partito</t>
   </si>
   <si>
@@ -182,9 +161,6 @@
     <t>Partito Comunista Cinese; Renmin Ribao; Hongqi</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Maoismo; Rivoluzione culturale</t>
-  </si>
-  <si>
     <t>La classe operaia deve esercitare la sua direzione in ogni campo</t>
   </si>
   <si>
@@ -203,9 +179,6 @@
     <t>Livorno</t>
   </si>
   <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Marxismo-leninismo; Fosco Dinucci</t>
-  </si>
-  <si>
     <t>Foto</t>
   </si>
   <si>
@@ -215,9 +188,6 @@
     <t>Renmin Ribao</t>
   </si>
   <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Marxismo-leninismo; Fosco Dinucci; Delegazione</t>
-  </si>
-  <si>
     <t>Osvaldo Pesce, Partito Comunista d'Italia (marxista-leninista), incontra il presidente Mao Zedong</t>
   </si>
   <si>
@@ -242,18 +212,12 @@
     <t>Catania</t>
   </si>
   <si>
-    <t>Unione dei Comunisti Italiani (marxisti-leninisti); Servire il Popolo; Volantino</t>
-  </si>
-  <si>
     <t>Delegazione delle Edizioni Oriente accolta dal Presidente Mao Zedong</t>
   </si>
   <si>
     <t>Edizioni Oriente</t>
   </si>
   <si>
-    <t>Edizioni Oriente; Delegazione</t>
-  </si>
-  <si>
     <t>https://archive.org/details/delegazione-edizioni-oriente</t>
   </si>
   <si>
@@ -284,9 +248,6 @@
     <t>https://archive.org/details/mao-tse-tung-citazioni-presidente-vinile</t>
   </si>
   <si>
-    <t>Partito comunista cinese; Rivoluzione culturale; Maoismo; Libretto rosso</t>
-  </si>
-  <si>
     <t>Signal</t>
   </si>
   <si>
@@ -299,9 +260,6 @@
     <t>Mao Zedong; Roberto Sassi</t>
   </si>
   <si>
-    <t>Maoismo</t>
-  </si>
-  <si>
     <t>Lavoro Politico no. 1</t>
   </si>
   <si>
@@ -371,15 +329,6 @@
     <t>AMI-0030</t>
   </si>
   <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Partito Comunista d'Italia (marxista-leninista) - linea rossa; Lavoro Politico; Maoismo; Marxismo-leninismo</t>
-  </si>
-  <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Lavoro politico; Maoismo; Marxismo-leninismo</t>
-  </si>
-  <si>
-    <t>Maoismo; Marxismo-leninismo</t>
-  </si>
-  <si>
     <t>Lavoro Politico</t>
   </si>
   <si>
@@ -461,13 +410,7 @@
     <t>Verona</t>
   </si>
   <si>
-    <t>Proveniente dall'Archivio Storico della Nuova Sinistra "Marco Pezzi"</t>
-  </si>
-  <si>
     <t>Sulla tattica contro l'imperialismo giapponese</t>
-  </si>
-  <si>
-    <t>Partito comunista cinese; Maoismo; Guerra civile cinese; Lunga marcia</t>
   </si>
   <si>
     <t>AMI-0031</t>
@@ -759,12 +702,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:Q51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:Q51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O51" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:O51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M51">
     <sortCondition ref="A1:A51"/>
   </sortState>
-  <tableColumns count="17">
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{2154B3EB-64E4-4E6D-8A0C-04D65D066E62}" name="ID"/>
     <tableColumn id="2" xr3:uid="{7C80280B-722C-4CED-A5F4-3F72F39F1DFC}" name="Titolo"/>
     <tableColumn id="3" xr3:uid="{42E23130-656A-4022-81E0-AF9117BAC245}" name="Organizzazione"/>
@@ -776,8 +719,6 @@
     <tableColumn id="8" xr3:uid="{53C6379A-4E02-4FD7-81E4-B9C49DBDC091}" name="Serie"/>
     <tableColumn id="14" xr3:uid="{399D2721-A407-40F0-B94F-3E9CC27ADD44}" name="Persone_collegate"/>
     <tableColumn id="12" xr3:uid="{2D107D6C-67CE-488E-A50C-DF88DD95D047}" name="Organizzazioni_collegate"/>
-    <tableColumn id="9" xr3:uid="{18ED1BDE-DA2B-4274-908B-BC06AD7B6402}" name="Keywords"/>
-    <tableColumn id="10" xr3:uid="{AEDEDEC1-9395-48B6-A4EF-01A581661641}" name="Note"/>
     <tableColumn id="11" xr3:uid="{575D6553-9BD2-40E4-8055-A706418FDCC7}" name="URL" dataCellStyle="Collegamento ipertestuale"/>
     <tableColumn id="13" xr3:uid="{ACF3617F-A15C-4BA2-B462-292C6FA369C1}" name="Nome_file" dataDxfId="0" dataCellStyle="Collegamento ipertestuale"/>
     <tableColumn id="16" xr3:uid="{0BDE9F47-E369-4064-B628-A58828AF6D96}" name="Nome_file_originale"/>
@@ -1104,12 +1045,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
     <col min="3" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
     <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="11" max="11" width="27.6640625" customWidth="1"/>
@@ -1118,7 +1060,7 @@
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1129,10 +1071,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1144,1449 +1086,1317 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>1969</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M2" s="5"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>1967</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>1968</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>1968</v>
       </c>
       <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>1968</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>1968</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>1968</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1969</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O9" s="5"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10">
         <v>1969</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11">
         <v>1970</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12">
         <v>1968</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13">
         <v>1968</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="F14">
         <v>1967</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="J14" t="s">
-        <v>163</v>
-      </c>
-      <c r="L14" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O14" s="5"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3">
         <v>25064</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="J15" t="s">
-        <v>166</v>
-      </c>
-      <c r="L15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F16" s="3">
         <v>25081</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="J16" t="s">
-        <v>164</v>
-      </c>
-      <c r="L16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3">
         <v>25479</v>
       </c>
       <c r="G17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" t="s">
+        <v>146</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" t="s">
-        <v>188</v>
-      </c>
-      <c r="J17" t="s">
-        <v>165</v>
-      </c>
-      <c r="L17" t="s">
-        <v>58</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="F18" s="3">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I18" t="s">
-        <v>188</v>
-      </c>
-      <c r="L18" t="s">
-        <v>67</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="O18" s="5"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F19" s="3">
         <v>23511</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>188</v>
-      </c>
-      <c r="L19" t="s">
-        <v>70</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>69</v>
       </c>
       <c r="F20">
         <v>1969</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
-      </c>
-      <c r="L20" t="s">
-        <v>81</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O20" s="5"/>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="F21">
         <v>1993</v>
       </c>
       <c r="G21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="I21" t="s">
-        <v>83</v>
-      </c>
-      <c r="L21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>86</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O21" s="5"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>100</v>
-      </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F22" s="4">
         <v>24746</v>
       </c>
       <c r="G22" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I22" t="s">
-        <v>187</v>
-      </c>
-      <c r="L22" t="s">
-        <v>112</v>
-      </c>
-      <c r="M22" t="s">
-        <v>140</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O22" s="5"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F23" s="4">
         <v>24777</v>
       </c>
       <c r="G23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I23" t="s">
-        <v>187</v>
-      </c>
-      <c r="L23" t="s">
-        <v>112</v>
-      </c>
-      <c r="M23" t="s">
-        <v>140</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O23" s="5"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F24" s="4">
         <v>24838</v>
       </c>
       <c r="G24" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I24" t="s">
-        <v>187</v>
-      </c>
-      <c r="L24" t="s">
-        <v>112</v>
-      </c>
-      <c r="M24" t="s">
-        <v>140</v>
-      </c>
-      <c r="N24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
         <v>121</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>138</v>
-      </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F25" s="4">
         <v>24869</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H25" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I25" t="s">
-        <v>187</v>
-      </c>
-      <c r="L25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M25" t="s">
-        <v>140</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="O25" s="5"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F26" s="4">
         <v>24898</v>
       </c>
       <c r="G26" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>187</v>
-      </c>
-      <c r="L26" t="s">
-        <v>112</v>
-      </c>
-      <c r="M26" t="s">
-        <v>140</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O26" s="5"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F27" s="4">
         <v>24959</v>
       </c>
       <c r="G27" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I27" t="s">
-        <v>187</v>
-      </c>
-      <c r="L27" t="s">
-        <v>111</v>
-      </c>
-      <c r="M27" t="s">
-        <v>140</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F28" s="4">
         <v>24990</v>
       </c>
       <c r="G28" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I28" t="s">
-        <v>187</v>
-      </c>
-      <c r="L28" t="s">
-        <v>111</v>
-      </c>
-      <c r="M28" t="s">
-        <v>140</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F29" s="4">
         <v>25082</v>
       </c>
       <c r="G29" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I29" t="s">
-        <v>187</v>
-      </c>
-      <c r="L29" t="s">
-        <v>111</v>
-      </c>
-      <c r="M29" t="s">
-        <v>140</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O29" s="5"/>
-      <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F30" s="4">
         <v>25173</v>
       </c>
       <c r="G30" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H30" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I30" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="K30" t="s">
-        <v>185</v>
-      </c>
-      <c r="L30" t="s">
-        <v>110</v>
-      </c>
-      <c r="M30" t="s">
-        <v>140</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O30" s="5"/>
-      <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31">
         <v>1968</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
-      </c>
-      <c r="L31" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O31" s="5"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32">
         <v>1968</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
-      </c>
-      <c r="L32" t="s">
-        <v>142</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O32" s="5"/>
-      <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="F33">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="J33" t="s">
-        <v>160</v>
-      </c>
-      <c r="L33" t="s">
-        <v>112</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3">
         <v>25063</v>
       </c>
       <c r="G34" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
         <v>169</v>
       </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="s">
-        <v>188</v>
-      </c>
       <c r="J34" t="s">
+        <v>151</v>
+      </c>
+      <c r="K34" t="s">
+        <v>158</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" t="s">
+        <v>155</v>
+      </c>
+      <c r="O34" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" t="s">
         <v>170</v>
       </c>
-      <c r="K34" t="s">
-        <v>177</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O34" s="5"/>
-      <c r="P34" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>176</v>
-      </c>
-      <c r="B35" t="s">
-        <v>189</v>
-      </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3">
         <v>25081</v>
       </c>
       <c r="G35" t="s">
+        <v>150</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
         <v>169</v>
       </c>
-      <c r="H35" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" t="s">
-        <v>188</v>
-      </c>
       <c r="J35" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O35" s="5"/>
-      <c r="P35" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" t="s">
+        <v>161</v>
+      </c>
+      <c r="O35" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F36" s="4">
         <v>25416</v>
       </c>
       <c r="G36" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="I36" t="s">
-        <v>188</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M36" s="5"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="F37">
         <v>1975</v>
       </c>
       <c r="G37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K37" t="s">
-        <v>157</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O37" s="5"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N38" s="1"/>
-      <c r="O38" s="5"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N39" s="1"/>
-      <c r="O39" s="5"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N40" s="1"/>
-      <c r="O40" s="5"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N41" s="1"/>
-      <c r="O41" s="5"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N42" s="1"/>
-      <c r="O42" s="5"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N43" s="1"/>
-      <c r="O43" s="5"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N44" s="1"/>
-      <c r="O44" s="5"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N45" s="1"/>
-      <c r="O45" s="5"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N46" s="1"/>
-      <c r="O46" s="5"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N47" s="1"/>
-      <c r="O47" s="5"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N48" s="1"/>
-      <c r="O48" s="5"/>
-    </row>
-    <row r="49" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N49" s="1"/>
-      <c r="O49" s="5"/>
-    </row>
-    <row r="50" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N50" s="1"/>
-      <c r="O50" s="5"/>
-    </row>
-    <row r="51" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N51" s="1"/>
-      <c r="O51" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M37" s="5"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L38" s="1"/>
+      <c r="M38" s="5"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L39" s="1"/>
+      <c r="M39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L40" s="1"/>
+      <c r="M40" s="5"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L41" s="1"/>
+      <c r="M41" s="5"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L42" s="1"/>
+      <c r="M42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L43" s="1"/>
+      <c r="M43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L44" s="1"/>
+      <c r="M44" s="5"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L45" s="1"/>
+      <c r="M45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L46" s="1"/>
+      <c r="M46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L47" s="1"/>
+      <c r="M47" s="5"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L48" s="1"/>
+      <c r="M48" s="5"/>
+    </row>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L49" s="1"/>
+      <c r="M49" s="5"/>
+    </row>
+    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L50" s="1"/>
+      <c r="M50" s="5"/>
+    </row>
+    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L51" s="1"/>
+      <c r="M51" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
-    <hyperlink ref="N3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
-    <hyperlink ref="N5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
-    <hyperlink ref="N6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
-    <hyperlink ref="N7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
-    <hyperlink ref="N8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
-    <hyperlink ref="N9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
-    <hyperlink ref="N10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
-    <hyperlink ref="N11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
-    <hyperlink ref="N4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
-    <hyperlink ref="N12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
-    <hyperlink ref="N13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
-    <hyperlink ref="N16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
-    <hyperlink ref="N18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
-    <hyperlink ref="N20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
-    <hyperlink ref="N27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
-    <hyperlink ref="N23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
-    <hyperlink ref="N30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
-    <hyperlink ref="N28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
-    <hyperlink ref="N29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
-    <hyperlink ref="N31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
-    <hyperlink ref="N24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
-    <hyperlink ref="N22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
-    <hyperlink ref="N21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
-    <hyperlink ref="N14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
-    <hyperlink ref="N25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
-    <hyperlink ref="N32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
-    <hyperlink ref="N15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
-    <hyperlink ref="N17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
-    <hyperlink ref="N19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
-    <hyperlink ref="N35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
-    <hyperlink ref="N36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{75651139-E161-458B-994F-5E49098574C4}"/>
+    <hyperlink ref="L3" r:id="rId2" xr:uid="{CD2184ED-A91F-4121-BCE4-6F5F57657BD3}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{3151CD6F-6360-48A0-8A96-C6CA7BFA87B6}"/>
+    <hyperlink ref="L6" r:id="rId4" xr:uid="{921C0161-13F9-4AB1-9943-F088E8D04C77}"/>
+    <hyperlink ref="L7" r:id="rId5" xr:uid="{FA209DF6-7529-4AE3-93C8-C5B93022C678}"/>
+    <hyperlink ref="L8" r:id="rId6" xr:uid="{38D827A5-F723-490A-9D42-AA029CF987C7}"/>
+    <hyperlink ref="L9" r:id="rId7" xr:uid="{5EB7D969-3FFF-442C-88FB-72DAAAA56076}"/>
+    <hyperlink ref="L10" r:id="rId8" xr:uid="{2268931D-446D-439B-9355-E2623ED61D92}"/>
+    <hyperlink ref="L11" r:id="rId9" xr:uid="{915763FF-0C45-48F3-9200-2017B4DABB1A}"/>
+    <hyperlink ref="L4" r:id="rId10" xr:uid="{1F0EF04E-FA12-4EEF-97A1-C7749706DB4F}"/>
+    <hyperlink ref="L12" r:id="rId11" xr:uid="{EEE35428-6F4A-4888-8DC3-236CD045A4C4}"/>
+    <hyperlink ref="L13" r:id="rId12" xr:uid="{CD26B191-DAB6-4841-BD26-BA331F3F2FD5}"/>
+    <hyperlink ref="L16" r:id="rId13" xr:uid="{611B58DF-00D2-4FCD-BFD9-E1CB142D4AEA}"/>
+    <hyperlink ref="L18" r:id="rId14" xr:uid="{E315CB92-B7FC-4525-A8A4-456D931C2BB8}"/>
+    <hyperlink ref="L20" r:id="rId15" xr:uid="{3F906912-676F-47CF-9E8F-84EE32703C48}"/>
+    <hyperlink ref="L27" r:id="rId16" xr:uid="{7831D5F3-4CB5-4DC2-85FF-55351DC060AF}"/>
+    <hyperlink ref="L23" r:id="rId17" xr:uid="{C44BCAC6-AD3C-4236-BA13-54D5B6646DBA}"/>
+    <hyperlink ref="L30" r:id="rId18" xr:uid="{1C36EE42-0FF0-41A2-839A-2670099D91D7}"/>
+    <hyperlink ref="L28" r:id="rId19" xr:uid="{4715435A-D915-48BB-86DC-7EC994B95D73}"/>
+    <hyperlink ref="L29" r:id="rId20" xr:uid="{2406BBFC-AD68-471A-A754-E12E8DE9162D}"/>
+    <hyperlink ref="L31" r:id="rId21" xr:uid="{D78D0483-589F-4A18-B9C0-398C7F732239}"/>
+    <hyperlink ref="L24" r:id="rId22" xr:uid="{10936D2F-E6BF-4F7D-A904-6C00D4AC1D80}"/>
+    <hyperlink ref="L22" r:id="rId23" xr:uid="{96A5CD88-6692-4767-A93B-E739158B6BAB}"/>
+    <hyperlink ref="L21" r:id="rId24" xr:uid="{19EDCFD9-D88E-4993-A4E8-9BBF5848488C}"/>
+    <hyperlink ref="L14" r:id="rId25" xr:uid="{4D1018A8-1C5E-49D0-97C9-8DB65D890705}"/>
+    <hyperlink ref="L25" r:id="rId26" xr:uid="{68852D62-7997-4DA4-B0D6-64A7F310DAA6}"/>
+    <hyperlink ref="L32" r:id="rId27" xr:uid="{D4F6FC2F-CB40-4FC7-8086-063D674E2E9A}"/>
+    <hyperlink ref="L15" r:id="rId28" xr:uid="{7245A84A-A98E-4172-84DF-6CB6DA1C660D}"/>
+    <hyperlink ref="L17" r:id="rId29" xr:uid="{A1444548-667F-44FF-A262-FB159B81D88D}"/>
+    <hyperlink ref="L19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
+    <hyperlink ref="L35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
+    <hyperlink ref="L36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId33"/>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF4837D-E236-4BD1-966F-109BEFBDAB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD33282-9015-44A6-9EA8-16022A95270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="181">
   <si>
     <t>ID</t>
   </si>
@@ -579,6 +579,9 @@
   </si>
   <si>
     <t>Bologna</t>
+  </si>
+  <si>
+    <t>Nuova Unità; Unione della gioventù comunista d’Italia (marxista-leninista)</t>
   </si>
 </sst>
 </file>
@@ -704,7 +707,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O51" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:O51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M51">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O51">
     <sortCondition ref="A1:A51"/>
   </sortState>
   <tableColumns count="15">
@@ -1054,6 +1057,7 @@
     <col min="6" max="6" width="10.77734375" customWidth="1"/>
     <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" customWidth="1"/>
     <col min="11" max="11" width="27.6640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="101.33203125" customWidth="1"/>
@@ -1115,7 +1119,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1149,7 +1153,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1183,7 +1187,7 @@
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1217,7 +1221,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1251,7 +1255,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1285,7 +1289,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1319,7 +1323,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1353,7 +1357,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1387,7 +1391,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1421,7 +1425,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1455,7 +1459,7 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -1489,7 +1493,7 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -1546,6 +1550,9 @@
       <c r="J14" t="s">
         <v>144</v>
       </c>
+      <c r="K14" t="s">
+        <v>180</v>
+      </c>
       <c r="L14" s="1" t="s">
         <v>109</v>
       </c>
@@ -1791,10 +1798,10 @@
         <v>73</v>
       </c>
       <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" t="s">
         <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>96</v>
       </c>
       <c r="F22" s="4">
         <v>24746</v>
@@ -1822,10 +1829,10 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" t="s">
         <v>121</v>
-      </c>
-      <c r="D23" t="s">
-        <v>96</v>
       </c>
       <c r="F23" s="4">
         <v>24777</v>
@@ -1853,10 +1860,10 @@
         <v>75</v>
       </c>
       <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" t="s">
         <v>121</v>
-      </c>
-      <c r="D24" t="s">
-        <v>96</v>
       </c>
       <c r="F24" s="4">
         <v>24838</v>
@@ -1884,10 +1891,10 @@
         <v>76</v>
       </c>
       <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
         <v>121</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
       </c>
       <c r="F25" s="4">
         <v>24869</v>
@@ -1915,10 +1922,10 @@
         <v>78</v>
       </c>
       <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s">
         <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>96</v>
       </c>
       <c r="F26" s="4">
         <v>24898</v>
@@ -1946,10 +1953,10 @@
         <v>77</v>
       </c>
       <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
         <v>121</v>
-      </c>
-      <c r="D27" t="s">
-        <v>96</v>
       </c>
       <c r="F27" s="4">
         <v>24959</v>
@@ -1977,10 +1984,10 @@
         <v>79</v>
       </c>
       <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" t="s">
         <v>121</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
       </c>
       <c r="F28" s="4">
         <v>24990</v>
@@ -2008,10 +2015,10 @@
         <v>80</v>
       </c>
       <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
         <v>121</v>
-      </c>
-      <c r="D29" t="s">
-        <v>96</v>
       </c>
       <c r="F29" s="4">
         <v>25082</v>
@@ -2024,6 +2031,9 @@
       </c>
       <c r="I29" t="s">
         <v>168</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>100</v>
@@ -2039,10 +2049,10 @@
         <v>81</v>
       </c>
       <c r="C30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s">
         <v>121</v>
-      </c>
-      <c r="D30" t="s">
-        <v>96</v>
       </c>
       <c r="F30" s="4">
         <v>25173</v>
@@ -2073,7 +2083,7 @@
         <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D31" t="s">
         <v>83</v>
@@ -2107,7 +2117,7 @@
         <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD33282-9015-44A6-9EA8-16022A95270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1127BA17-E587-4625-BBA2-CC1B013687AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="4140" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="189">
   <si>
     <t>ID</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Circolare del 16 maggio 1966 - Un grande documento storico</t>
   </si>
   <si>
-    <t>Partito Comunista Cinese; Renmin Ribao; Hongqi</t>
-  </si>
-  <si>
     <t>La classe operaia deve esercitare la sua direzione in ogni campo</t>
   </si>
   <si>
@@ -563,9 +560,6 @@
     <t>Roma</t>
   </si>
   <si>
-    <t>https://archive.org/details/in-caso-di-golpe/mode/2up</t>
-  </si>
-  <si>
     <t>In caso di golpe: Manuale teorico-pratico per il cittadino, di resistenza totale e di guerra di popolo, di guerriglia e di controguerriglia</t>
   </si>
   <si>
@@ -582,6 +576,36 @@
   </si>
   <si>
     <t>Nuova Unità; Unione della gioventù comunista d’Italia (marxista-leninista)</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/in-caso-di-golpe-AMI/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0037</t>
+  </si>
+  <si>
+    <t>AMI-0038</t>
+  </si>
+  <si>
+    <t>Comitato Centrale del PCC</t>
+  </si>
+  <si>
+    <t>I compiti del Partito Comunista Cinese nel periodo della resistenza al Giappone</t>
+  </si>
+  <si>
+    <t>Comunicato della seconda sessione plenaria del IX Comitato Centrale del Partito Comunista Cinese</t>
+  </si>
+  <si>
+    <t>Mao Zedong; Lin Biao</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/comunicato-ix-cc/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/compiti-guerra-giapponese/mode/2up</t>
+  </si>
+  <si>
+    <t>Comitato Centrale del PCC; Renmin Ribao; Hongqi</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1093,22 +1117,22 @@
         <v>14</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -1119,7 +1143,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1140,7 +1164,7 @@
         <v>15</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="2"/>
@@ -1153,7 +1177,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1174,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2"/>
@@ -1187,7 +1211,7 @@
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1208,7 +1232,7 @@
         <v>15</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="2"/>
@@ -1221,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1242,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="2"/>
@@ -1255,7 +1279,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1289,7 +1313,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1310,7 +1334,7 @@
         <v>15</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="2"/>
@@ -1323,7 +1347,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1344,7 +1368,7 @@
         <v>15</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="2"/>
@@ -1357,7 +1381,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1378,7 +1402,7 @@
         <v>15</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="2"/>
@@ -1391,7 +1415,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1412,7 +1436,7 @@
         <v>15</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="2"/>
@@ -1425,7 +1449,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1446,7 +1470,7 @@
         <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="2"/>
@@ -1459,10 +1483,10 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>188</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -1479,8 +1503,11 @@
       <c r="I12" t="s">
         <v>15</v>
       </c>
+      <c r="K12" t="s">
+        <v>157</v>
+      </c>
       <c r="L12" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="2"/>
@@ -1490,13 +1517,13 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" t="s">
         <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -1514,26 +1541,26 @@
         <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>43</v>
       </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F14">
         <v>1967</v>
@@ -1542,235 +1569,235 @@
         <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
         <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
       </c>
       <c r="F15" s="3">
         <v>25064</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s">
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
       </c>
       <c r="F16" s="3">
         <v>25081</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
         <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3">
         <v>25479</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F18" s="3">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" s="3">
         <v>23511</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
         <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20">
         <v>1969</v>
       </c>
       <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I20" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" t="s">
         <v>71</v>
       </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F21">
         <v>1993</v>
@@ -1779,314 +1806,314 @@
         <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F22" s="4">
         <v>24746</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F23" s="4">
         <v>24777</v>
       </c>
       <c r="G23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="4">
         <v>24838</v>
       </c>
       <c r="G24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="4">
         <v>24869</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" s="4">
         <v>24898</v>
       </c>
       <c r="G26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="4">
         <v>24959</v>
       </c>
       <c r="G27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F28" s="4">
         <v>24990</v>
       </c>
       <c r="G28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="4">
         <v>25082</v>
       </c>
       <c r="G29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="4">
         <v>25173</v>
       </c>
       <c r="G30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" t="s">
-        <v>83</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -2104,20 +2131,20 @@
         <v>15</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -2138,88 +2165,88 @@
         <v>15</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" t="s">
         <v>137</v>
-      </c>
-      <c r="C33" t="s">
-        <v>138</v>
       </c>
       <c r="F33">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
+        <v>139</v>
+      </c>
+      <c r="I33" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33" t="s">
         <v>140</v>
       </c>
-      <c r="I33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="L33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" t="s">
         <v>148</v>
       </c>
-      <c r="B34" t="s">
-        <v>149</v>
-      </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3">
         <v>25063</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H34" t="s">
         <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K34" t="s">
+        <v>157</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="K34" t="s">
-        <v>158</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" t="s">
         <v>157</v>
-      </c>
-      <c r="B35" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" t="s">
-        <v>158</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -2228,73 +2255,73 @@
         <v>25081</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H35" t="s">
         <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J35" t="s">
+        <v>158</v>
+      </c>
+      <c r="K35" t="s">
+        <v>42</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="K35" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" t="s">
+        <v>160</v>
+      </c>
+      <c r="O35" t="s">
         <v>161</v>
-      </c>
-      <c r="O35" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" t="s">
         <v>163</v>
       </c>
-      <c r="B36" t="s">
-        <v>164</v>
-      </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F36" s="4">
         <v>25416</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" t="s">
         <v>171</v>
-      </c>
-      <c r="B37" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" t="s">
-        <v>172</v>
       </c>
       <c r="F37">
         <v>1975</v>
@@ -2303,25 +2330,86 @@
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L38" s="1"/>
+      <c r="A38" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38">
+        <v>1968</v>
+      </c>
+      <c r="G38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L39" s="1"/>
+      <c r="A39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39">
+        <v>1970</v>
+      </c>
+      <c r="G39" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -2407,11 +2495,14 @@
     <hyperlink ref="L19" r:id="rId30" xr:uid="{EAA76073-A10F-44D7-BE5A-B85456ABE721}"/>
     <hyperlink ref="L35" r:id="rId31" xr:uid="{F6D5DE52-9CF3-4FC4-AA40-6B826ADFDEE9}"/>
     <hyperlink ref="L36" r:id="rId32" xr:uid="{584810A0-C3EE-4DFD-B2C9-186C6BD968BB}"/>
+    <hyperlink ref="L37" r:id="rId33" xr:uid="{0E5E3D88-89AF-4D23-BCEF-E14D85ECF6DA}"/>
+    <hyperlink ref="L39" r:id="rId34" xr:uid="{EE37606F-693C-4D2A-BD98-092CA484F793}"/>
+    <hyperlink ref="L38" r:id="rId35" xr:uid="{92A62FBF-7C57-4C16-B112-96E72C0BCEC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId33"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId36"/>
   <tableParts count="1">
-    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1127BA17-E587-4625-BBA2-CC1B013687AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29CB35-2831-42E1-A6C5-D0A65775B17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="196">
   <si>
     <t>ID</t>
   </si>
@@ -606,6 +606,27 @@
   </si>
   <si>
     <t>Comitato Centrale del PCC; Renmin Ribao; Hongqi</t>
+  </si>
+  <si>
+    <t>AMI-0039</t>
+  </si>
+  <si>
+    <t>AMI-0040</t>
+  </si>
+  <si>
+    <t>Renmin Ribao; Jiefangjun Bao; Hongqi</t>
+  </si>
+  <si>
+    <t>Il Presidente Mao Tse-tung sulla Guerra Popolare</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/sulla-guerra-popolare/mode/2up</t>
+  </si>
+  <si>
+    <t>I membri del Partito Comunista devono essere elementi avanzati del proletariato</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/membri-del-partito-avanzati/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -2413,11 +2434,69 @@
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L40" s="1"/>
+      <c r="A40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40">
+        <v>1968</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L41" s="1"/>
+      <c r="A41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41">
+        <v>1970</v>
+      </c>
+      <c r="G41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -2498,11 +2577,13 @@
     <hyperlink ref="L37" r:id="rId33" xr:uid="{0E5E3D88-89AF-4D23-BCEF-E14D85ECF6DA}"/>
     <hyperlink ref="L39" r:id="rId34" xr:uid="{EE37606F-693C-4D2A-BD98-092CA484F793}"/>
     <hyperlink ref="L38" r:id="rId35" xr:uid="{92A62FBF-7C57-4C16-B112-96E72C0BCEC5}"/>
+    <hyperlink ref="L40" r:id="rId36" xr:uid="{3CDC56C8-A737-48A5-AE4B-43C2A68B4039}"/>
+    <hyperlink ref="L41" r:id="rId37" xr:uid="{09C4D1EB-352A-4261-B5EC-7B28FF918427}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId36"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId38"/>
   <tableParts count="1">
-    <tablePart r:id="rId37"/>
+    <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29CB35-2831-42E1-A6C5-D0A65775B17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD543C7-8C34-430F-B89D-73D0FEBCDA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="206">
   <si>
     <t>ID</t>
   </si>
@@ -627,6 +627,36 @@
   </si>
   <si>
     <t>https://archive.org/details/membri-del-partito-avanzati/mode/2up</t>
+  </si>
+  <si>
+    <t>Testi del maoismo; Libretti rossi</t>
+  </si>
+  <si>
+    <t>AMI-0041</t>
+  </si>
+  <si>
+    <t>AMI-0042</t>
+  </si>
+  <si>
+    <t>Feltrinelli</t>
+  </si>
+  <si>
+    <t>Libretti rossi</t>
+  </si>
+  <si>
+    <t>Longanesi &amp; C.</t>
+  </si>
+  <si>
+    <t>Giorgio Zucchetti</t>
+  </si>
+  <si>
+    <t>Citazioni: Il breviario delle guardie rosse</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/citazioni-del-presidente-mao-tse-tung-feltrinelli/mode/2up</t>
+  </si>
+  <si>
+    <t>Associazione Italia-Cina</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>119</v>
@@ -2459,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>193</v>
@@ -2500,10 +2530,66 @@
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L42" s="1"/>
+      <c r="A42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>199</v>
+      </c>
+      <c r="F42">
+        <v>1968</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>164</v>
+      </c>
+      <c r="I42" t="s">
+        <v>200</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="M42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43">
+        <v>1967</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s">
+        <v>164</v>
+      </c>
+      <c r="I43" t="s">
+        <v>200</v>
+      </c>
+      <c r="J43" t="s">
+        <v>202</v>
+      </c>
+      <c r="K43" t="s">
+        <v>205</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
     </row>
@@ -2579,11 +2665,12 @@
     <hyperlink ref="L38" r:id="rId35" xr:uid="{92A62FBF-7C57-4C16-B112-96E72C0BCEC5}"/>
     <hyperlink ref="L40" r:id="rId36" xr:uid="{3CDC56C8-A737-48A5-AE4B-43C2A68B4039}"/>
     <hyperlink ref="L41" r:id="rId37" xr:uid="{09C4D1EB-352A-4261-B5EC-7B28FF918427}"/>
+    <hyperlink ref="L42" r:id="rId38" xr:uid="{EA325D15-4DFD-4D7B-9E45-920024DE00BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId38"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId39"/>
   <tableParts count="1">
-    <tablePart r:id="rId39"/>
+    <tablePart r:id="rId40"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD543C7-8C34-430F-B89D-73D0FEBCDA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B383878-D699-45D2-BE2D-FC8F23FB2BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="207">
   <si>
     <t>ID</t>
   </si>
@@ -657,6 +657,9 @@
   </si>
   <si>
     <t>Associazione Italia-Cina</t>
+  </si>
+  <si>
+    <t>Citazioni del presidente Mao Tse-tung: Il libro delle guardie rosse</t>
   </si>
 </sst>
 </file>
@@ -2534,7 +2537,7 @@
         <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B383878-D699-45D2-BE2D-FC8F23FB2BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A442854F-6A5C-4EBC-B026-45882100B8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="208">
   <si>
     <t>ID</t>
   </si>
@@ -660,6 +660,9 @@
   </si>
   <si>
     <t>Citazioni del presidente Mao Tse-tung: Il libro delle guardie rosse</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/breviario-delle-guardie-rosse/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -2593,7 +2596,9 @@
       <c r="K43" t="s">
         <v>205</v>
       </c>
-      <c r="L43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="M43" s="5"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -2669,11 +2674,12 @@
     <hyperlink ref="L40" r:id="rId36" xr:uid="{3CDC56C8-A737-48A5-AE4B-43C2A68B4039}"/>
     <hyperlink ref="L41" r:id="rId37" xr:uid="{09C4D1EB-352A-4261-B5EC-7B28FF918427}"/>
     <hyperlink ref="L42" r:id="rId38" xr:uid="{EA325D15-4DFD-4D7B-9E45-920024DE00BE}"/>
+    <hyperlink ref="L43" r:id="rId39" xr:uid="{D1862510-187C-4AFE-9567-9B4F98379069}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId39"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId40"/>
   <tableParts count="1">
-    <tablePart r:id="rId40"/>
+    <tablePart r:id="rId41"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A442854F-6A5C-4EBC-B026-45882100B8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BFA179-C059-4D6C-B1EA-4E04D380B639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="214">
   <si>
     <t>ID</t>
   </si>
@@ -344,9 +344,6 @@
     <t>https://archive.org/details/lavoro-politico-11-12/mode/2up</t>
   </si>
   <si>
-    <t>https://archive.org/details/la-bussola-che-guida//mode/2up</t>
-  </si>
-  <si>
     <t>https://archive.org/details/lavoro-politico-07//mode/2up</t>
   </si>
   <si>
@@ -365,9 +362,6 @@
     <t>https://archive.org/details/studenti-ed-intellettuali-ciclostilato-uci-m-l/mode/2up</t>
   </si>
   <si>
-    <t>https://archive.org/details/statuto-pcdi/mode/2up</t>
-  </si>
-  <si>
     <t>https://archive.org/details/la-classe-operai-deve-esercitare-la-sua-direzione-in-ogni-cam/mode/2up</t>
   </si>
   <si>
@@ -663,6 +657,30 @@
   </si>
   <si>
     <t>https://archive.org/details/breviario-delle-guardie-rosse/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0043</t>
+  </si>
+  <si>
+    <t>Sulla Nuova Democrazia</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/sulla-nuova-democrazia/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/statuto-pcdiml/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0044</t>
+  </si>
+  <si>
+    <t>Analisi delle classi nella società cinese</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/bussola-popoli-rivoluzionari/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/analisi-delle-classi/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1177,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1174,22 +1192,22 @@
         <v>14</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -1200,7 +1218,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1218,10 +1236,10 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="2"/>
@@ -1234,7 +1252,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1255,7 +1273,7 @@
         <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2"/>
@@ -1268,7 +1286,7 @@
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1289,7 +1307,7 @@
         <v>15</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="2"/>
@@ -1302,7 +1320,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1323,7 +1341,7 @@
         <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="2"/>
@@ -1336,7 +1354,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1370,7 +1388,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1391,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="2"/>
@@ -1404,7 +1422,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1425,7 +1443,7 @@
         <v>15</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="2"/>
@@ -1438,7 +1456,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1459,7 +1477,7 @@
         <v>15</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="2"/>
@@ -1472,7 +1490,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1493,7 +1511,7 @@
         <v>15</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="2"/>
@@ -1506,7 +1524,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1527,7 +1545,7 @@
         <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="2"/>
@@ -1540,10 +1558,10 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -1561,10 +1579,10 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="2"/>
@@ -1577,7 +1595,7 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
@@ -1598,7 +1616,7 @@
         <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="2"/>
@@ -1617,7 +1635,7 @@
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F14">
         <v>1967</v>
@@ -1629,16 +1647,16 @@
         <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="2"/>
@@ -1666,16 +1684,16 @@
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N15" s="2"/>
     </row>
@@ -1702,16 +1720,16 @@
         <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N16" s="2"/>
     </row>
@@ -1738,16 +1756,16 @@
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -1762,22 +1780,22 @@
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F18" s="3">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
         <v>55</v>
       </c>
       <c r="I18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="2"/>
@@ -1805,13 +1823,13 @@
         <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>58</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N19" s="2"/>
     </row>
@@ -1854,7 +1872,7 @@
         <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F21">
         <v>1993</v>
@@ -1863,13 +1881,13 @@
         <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
         <v>69</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="2"/>
@@ -1885,22 +1903,22 @@
         <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F22" s="4">
         <v>24746</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="2"/>
@@ -1916,22 +1934,22 @@
         <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F23" s="4">
         <v>24777</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="2"/>
@@ -1947,22 +1965,22 @@
         <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F24" s="4">
         <v>24838</v>
       </c>
       <c r="G24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="2"/>
@@ -1978,19 +1996,19 @@
         <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" s="4">
         <v>24869</v>
       </c>
       <c r="G25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>96</v>
@@ -2009,19 +2027,19 @@
         <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F26" s="4">
         <v>24898</v>
       </c>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>97</v>
@@ -2040,22 +2058,22 @@
         <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F27" s="4">
         <v>24959</v>
       </c>
       <c r="G27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="2"/>
@@ -2071,19 +2089,19 @@
         <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F28" s="4">
         <v>24990</v>
       </c>
       <c r="G28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>98</v>
@@ -2102,19 +2120,19 @@
         <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F29" s="4">
         <v>25082</v>
       </c>
       <c r="G29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K29" t="s">
         <v>42</v>
@@ -2136,22 +2154,22 @@
         <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F30" s="4">
         <v>25173</v>
       </c>
       <c r="G30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>100</v>
@@ -2167,7 +2185,7 @@
         <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
         <v>82</v>
@@ -2188,20 +2206,20 @@
         <v>15</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>101</v>
+        <v>212</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -2222,46 +2240,46 @@
         <v>15</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F33">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" t="s">
+        <v>166</v>
+      </c>
+      <c r="J33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I33" t="s">
-        <v>168</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="M33" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
@@ -2270,40 +2288,40 @@
         <v>25063</v>
       </c>
       <c r="G34" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H34" t="s">
         <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O34" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -2312,37 +2330,37 @@
         <v>25081</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H35" t="s">
         <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K35" t="s">
         <v>42</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O35" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
         <v>54</v>
@@ -2351,34 +2369,34 @@
         <v>25416</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" t="s">
+        <v>166</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I36" t="s">
-        <v>168</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="M36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F37">
         <v>1975</v>
@@ -2387,28 +2405,28 @@
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I37" t="s">
         <v>69</v>
       </c>
       <c r="K37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2429,22 +2447,22 @@
         <v>15</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
@@ -2462,22 +2480,22 @@
         <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B40" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2495,25 +2513,25 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
@@ -2531,22 +2549,22 @@
         <v>15</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F42">
         <v>1968</v>
@@ -2555,28 +2573,28 @@
         <v>9</v>
       </c>
       <c r="H42" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I42" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F43">
         <v>1967</v>
@@ -2585,28 +2603,86 @@
         <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I43" t="s">
+        <v>198</v>
+      </c>
+      <c r="J43" t="s">
         <v>200</v>
       </c>
-      <c r="J43" t="s">
-        <v>202</v>
-      </c>
       <c r="K43" t="s">
+        <v>203</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="M43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" t="s">
         <v>207</v>
       </c>
-      <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L44" s="1"/>
+      <c r="C44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44">
+        <v>1968</v>
+      </c>
+      <c r="G44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="M44" s="5"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L45" s="1"/>
+      <c r="A45" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C45" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45">
+        <v>1967</v>
+      </c>
+      <c r="G45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="M45" s="5"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
@@ -2675,11 +2751,13 @@
     <hyperlink ref="L41" r:id="rId37" xr:uid="{09C4D1EB-352A-4261-B5EC-7B28FF918427}"/>
     <hyperlink ref="L42" r:id="rId38" xr:uid="{EA325D15-4DFD-4D7B-9E45-920024DE00BE}"/>
     <hyperlink ref="L43" r:id="rId39" xr:uid="{D1862510-187C-4AFE-9567-9B4F98379069}"/>
+    <hyperlink ref="L44" r:id="rId40" xr:uid="{B284CC2D-C090-4C37-A618-E0D93BA9D029}"/>
+    <hyperlink ref="L45" r:id="rId41" xr:uid="{64AB231A-9826-4296-9447-2E5BE606BA1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId40"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId42"/>
   <tableParts count="1">
-    <tablePart r:id="rId41"/>
+    <tablePart r:id="rId43"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BFA179-C059-4D6C-B1EA-4E04D380B639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DEA31F-DF34-4A7E-8183-C181D8D47456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="231">
   <si>
     <t>ID</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Serie</t>
   </si>
   <si>
-    <t>Testi del maoismo</t>
-  </si>
-  <si>
     <t>Sulla giusta soluzione delle contraddizioni in seno al popolo</t>
   </si>
   <si>
@@ -623,9 +620,6 @@
     <t>https://archive.org/details/membri-del-partito-avanzati/mode/2up</t>
   </si>
   <si>
-    <t>Testi del maoismo; Libretti rossi</t>
-  </si>
-  <si>
     <t>AMI-0041</t>
   </si>
   <si>
@@ -681,6 +675,63 @@
   </si>
   <si>
     <t>https://archive.org/details/analisi-delle-classi/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0045</t>
+  </si>
+  <si>
+    <t>AMI-0046</t>
+  </si>
+  <si>
+    <t>AMI-0047</t>
+  </si>
+  <si>
+    <t>La questione dell'indipendenza e dell'autonomia nel Fronte Unito</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/questione-dellindipendenza/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-monti-chingkang/mode/2up</t>
+  </si>
+  <si>
+    <t>La lotta sui monti Chingkang</t>
+  </si>
+  <si>
+    <t>Sulla pratica</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/sulla-pratica/mode/2up</t>
+  </si>
+  <si>
+    <t>Materiali cinesi; Fondamenti del maoismo</t>
+  </si>
+  <si>
+    <t>Materiali cinesi; Libretti rossi</t>
+  </si>
+  <si>
+    <t>Materiali cinesi</t>
+  </si>
+  <si>
+    <t>Materiali cinesi; Fondamenti del maoismo; Libretti rossi</t>
+  </si>
+  <si>
+    <t>AMI-0048</t>
+  </si>
+  <si>
+    <t>Rapporto d'inchiesta sul movimento contadino nello Hunan</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/inchiesta-movimento-contadino-hunan/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0049</t>
+  </si>
+  <si>
+    <t>Sulla contraddizione</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/sulla-contraddizione/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1192,22 +1243,22 @@
         <v>14</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -1218,7 +1269,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1236,23 +1287,23 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1264,29 +1315,29 @@
         <v>1967</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1298,29 +1349,29 @@
         <v>1968</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1332,29 +1383,29 @@
         <v>1968</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1366,29 +1417,29 @@
         <v>1968</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1400,29 +1451,29 @@
         <v>1968</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1434,29 +1485,29 @@
         <v>1968</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1468,29 +1519,29 @@
         <v>1969</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1502,29 +1553,29 @@
         <v>1969</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1536,32 +1587,32 @@
         <v>1970</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -1570,35 +1621,35 @@
         <v>1968</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
         <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="K12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -1607,272 +1658,272 @@
         <v>1968</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F14">
         <v>1967</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
       </c>
       <c r="F15" s="3">
         <v>25064</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
       </c>
       <c r="F16" s="3">
         <v>25081</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H16" t="s">
         <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="3">
         <v>25479</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s">
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F18" s="3">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
         <v>56</v>
       </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3">
         <v>23511</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
         <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20">
         <v>1969</v>
       </c>
       <c r="G20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I20" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
         <v>70</v>
       </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F21">
         <v>1993</v>
@@ -1881,314 +1932,314 @@
         <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F22" s="4">
         <v>24746</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="4">
         <v>24777</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F24" s="4">
         <v>24838</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F25" s="4">
         <v>24869</v>
       </c>
       <c r="G25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F26" s="4">
         <v>24898</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="4">
         <v>24959</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F28" s="4">
         <v>24990</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="4">
         <v>25082</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30" s="4">
         <v>25173</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" t="s">
         <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" t="s">
-        <v>82</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -2197,29 +2248,29 @@
         <v>1968</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
         <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -2231,97 +2282,97 @@
         <v>1968</v>
       </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" t="s">
         <v>134</v>
-      </c>
-      <c r="C33" t="s">
-        <v>135</v>
       </c>
       <c r="F33">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" t="s">
+        <v>165</v>
+      </c>
+      <c r="J33" t="s">
         <v>137</v>
       </c>
-      <c r="I33" t="s">
-        <v>166</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="L33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" t="s">
         <v>145</v>
       </c>
-      <c r="B34" t="s">
-        <v>146</v>
-      </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F34" s="3">
         <v>25063</v>
       </c>
       <c r="G34" t="s">
+        <v>146</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>165</v>
+      </c>
+      <c r="J34" t="s">
         <v>147</v>
       </c>
-      <c r="H34" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" t="s">
-        <v>166</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
+        <v>154</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="K34" t="s">
-        <v>155</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
         <v>154</v>
-      </c>
-      <c r="B35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" t="s">
-        <v>155</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -2330,73 +2381,73 @@
         <v>25081</v>
       </c>
       <c r="G35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H35" t="s">
         <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J35" t="s">
+        <v>155</v>
+      </c>
+      <c r="K35" t="s">
+        <v>41</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="K35" t="s">
-        <v>42</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" t="s">
+        <v>157</v>
+      </c>
+      <c r="O35" t="s">
         <v>158</v>
-      </c>
-      <c r="O35" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" t="s">
         <v>160</v>
       </c>
-      <c r="B36" t="s">
-        <v>161</v>
-      </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="4">
         <v>25416</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
         <v>168</v>
-      </c>
-      <c r="B37" t="s">
-        <v>171</v>
-      </c>
-      <c r="C37" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" t="s">
-        <v>169</v>
       </c>
       <c r="F37">
         <v>1975</v>
@@ -2405,28 +2456,28 @@
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2438,31 +2489,31 @@
         <v>1968</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" t="s">
+        <v>181</v>
+      </c>
+      <c r="C39" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" t="s">
         <v>179</v>
-      </c>
-      <c r="B39" t="s">
-        <v>182</v>
-      </c>
-      <c r="C39" t="s">
-        <v>155</v>
-      </c>
-      <c r="D39" t="s">
-        <v>180</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
@@ -2471,31 +2522,31 @@
         <v>1970</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
         <v>10</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="J39" t="s">
+        <v>182</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2513,25 +2564,25 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" t="s">
         <v>188</v>
-      </c>
-      <c r="B41" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" t="s">
-        <v>155</v>
-      </c>
-      <c r="D41" t="s">
-        <v>189</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
@@ -2540,31 +2591,31 @@
         <v>1970</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
         <v>10</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>1968</v>
@@ -2573,28 +2624,28 @@
         <v>9</v>
       </c>
       <c r="H42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I42" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F43">
         <v>1967</v>
@@ -2603,31 +2654,31 @@
         <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I43" t="s">
+        <v>196</v>
+      </c>
+      <c r="J43" t="s">
         <v>198</v>
       </c>
-      <c r="J43" t="s">
-        <v>200</v>
-      </c>
       <c r="K43" t="s">
+        <v>201</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="M43" s="5"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2639,28 +2690,28 @@
         <v>1968</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M44" s="5"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
@@ -2672,40 +2723,185 @@
         <v>1967</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
         <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L45" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="M45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46">
+        <v>1968</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" t="s">
+        <v>221</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="M46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>213</v>
       </c>
-      <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L46" s="1"/>
-      <c r="M46" s="5"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L47" s="1"/>
+      <c r="B47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C47" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47">
+        <v>1969</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" t="s">
+        <v>223</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="M47" s="5"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L48" s="1"/>
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48">
+        <v>1971</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>223</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="M48" s="5"/>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L49" s="1"/>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>225</v>
+      </c>
+      <c r="B49" t="s">
+        <v>226</v>
+      </c>
+      <c r="C49" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49">
+        <v>1968</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>221</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L50" s="1"/>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>228</v>
+      </c>
+      <c r="B50" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50">
+        <v>1968</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" t="s">
+        <v>221</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
     </row>
@@ -2753,11 +2949,16 @@
     <hyperlink ref="L43" r:id="rId39" xr:uid="{D1862510-187C-4AFE-9567-9B4F98379069}"/>
     <hyperlink ref="L44" r:id="rId40" xr:uid="{B284CC2D-C090-4C37-A618-E0D93BA9D029}"/>
     <hyperlink ref="L45" r:id="rId41" xr:uid="{64AB231A-9826-4296-9447-2E5BE606BA1E}"/>
+    <hyperlink ref="L48" r:id="rId42" xr:uid="{18E2E14E-CDBF-4330-866C-3A0D029555BF}"/>
+    <hyperlink ref="L47" r:id="rId43" xr:uid="{5BC73287-8866-4980-B190-213727E36300}"/>
+    <hyperlink ref="L46" r:id="rId44" xr:uid="{B78DC2C8-7501-489D-BB42-D0107A7FE548}"/>
+    <hyperlink ref="L49" r:id="rId45" xr:uid="{B4D3A143-EE84-4718-A4A3-C6F910195439}"/>
+    <hyperlink ref="L50" r:id="rId46" xr:uid="{2DB9E3D6-5030-499E-A349-B7348A4E0746}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId42"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId47"/>
   <tableParts count="1">
-    <tablePart r:id="rId43"/>
+    <tablePart r:id="rId48"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DEA31F-DF34-4A7E-8183-C181D8D47456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48A04E0-D598-46BF-AC5A-82191B147B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="242">
   <si>
     <t>ID</t>
   </si>
@@ -732,6 +732,39 @@
   </si>
   <si>
     <t>https://archive.org/details/sulla-contraddizione/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0050</t>
+  </si>
+  <si>
+    <t>AMI-0051</t>
+  </si>
+  <si>
+    <t>Problemi strategici della guerra rivoluzionaria in Cina</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/problemi-strategici-della-guerra-rivoluzionaria/mode/2up</t>
+  </si>
+  <si>
+    <t>Rapporto alla seconda sessione plenaria del settimo Comitato Centrale del Partito Comunista Cinese</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/rapporto-seconda-sessione-plenaria/mode/2up</t>
+  </si>
+  <si>
+    <t>Avanguardia Proletaria Maoista</t>
+  </si>
+  <si>
+    <t>Biblioteca dell'Avanguardia Proletaria</t>
+  </si>
+  <si>
+    <t>Gli studenti alleati del proletariato nella lotta rivoluzionaria in Italia</t>
+  </si>
+  <si>
+    <t>AMI-0052</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/studenti-alleati-proletariato/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -855,8 +888,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:O51" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O53" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:O53" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O51">
     <sortCondition ref="A1:A51"/>
   </sortState>
@@ -1198,9 +1231,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
     <col min="3" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
@@ -1209,8 +1243,8 @@
     <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="10" max="10" width="22.44140625" customWidth="1"/>
     <col min="11" max="11" width="27.6640625" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" customWidth="1"/>
-    <col min="13" max="13" width="101.33203125" customWidth="1"/>
+    <col min="12" max="12" width="78.44140625" customWidth="1"/>
+    <col min="13" max="13" width="38.21875" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2902,8 +2936,103 @@
       <c r="M50" s="5"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L51" s="1"/>
+      <c r="A51" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51">
+        <v>1968</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" t="s">
+        <v>221</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="M51" s="5"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52">
+        <v>1968</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" t="s">
+        <v>223</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="M52" s="5"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" t="s">
+        <v>237</v>
+      </c>
+      <c r="E53" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53">
+        <v>1969</v>
+      </c>
+      <c r="G53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" t="s">
+        <v>161</v>
+      </c>
+      <c r="I53" t="s">
+        <v>165</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M53" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2954,11 +3083,14 @@
     <hyperlink ref="L46" r:id="rId44" xr:uid="{B78DC2C8-7501-489D-BB42-D0107A7FE548}"/>
     <hyperlink ref="L49" r:id="rId45" xr:uid="{B4D3A143-EE84-4718-A4A3-C6F910195439}"/>
     <hyperlink ref="L50" r:id="rId46" xr:uid="{2DB9E3D6-5030-499E-A349-B7348A4E0746}"/>
+    <hyperlink ref="L51" r:id="rId47" xr:uid="{81DF7415-74A4-4A5B-BEF1-69F35D75A991}"/>
+    <hyperlink ref="L52" r:id="rId48" xr:uid="{6D6C9EBD-C509-45AC-AD32-2A67AD2727AD}"/>
+    <hyperlink ref="L53" r:id="rId49" xr:uid="{A01892A1-954B-41E4-B4CB-95523808FE8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId47"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId50"/>
   <tableParts count="1">
-    <tablePart r:id="rId48"/>
+    <tablePart r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48A04E0-D598-46BF-AC5A-82191B147B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215150F6-4860-4BB6-BF41-55F4F3B4897C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="247">
   <si>
     <t>ID</t>
   </si>
@@ -765,6 +765,21 @@
   </si>
   <si>
     <t>https://archive.org/details/studenti-alleati-proletariato/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0053</t>
+  </si>
+  <si>
+    <t>Cinisello Balsamo</t>
+  </si>
+  <si>
+    <t>Partito Comunista (marxista-leninista) Italiano</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/volantino-congresso-di-fondazione-pcm-l-i/mode/2up</t>
+  </si>
+  <si>
+    <t>Sosteniamo il Congresso di fondazione del PARTITO COMUNISTA (marxista-leninista) ITALIANO per fare l'Italia rossa e socialista come la Cina di Mao</t>
   </si>
 </sst>
 </file>
@@ -888,8 +903,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O53" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:O53" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}" name="Tabella2" displayName="Tabella2" ref="A1:O132" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:O132" xr:uid="{27B22AD5-AC5E-42EE-98AF-49D8C6FF315D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O51">
     <sortCondition ref="A1:A51"/>
   </sortState>
@@ -1231,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342C46E2-AB3D-4CAD-AFB0-E7E2D6732CC9}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3033,6 +3048,348 @@
         <v>241</v>
       </c>
       <c r="M53" s="5"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>242</v>
+      </c>
+      <c r="B54" t="s">
+        <v>246</v>
+      </c>
+      <c r="C54" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54">
+        <v>1972</v>
+      </c>
+      <c r="G54" t="s">
+        <v>123</v>
+      </c>
+      <c r="H54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I54" t="s">
+        <v>165</v>
+      </c>
+      <c r="K54" t="s">
+        <v>244</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="M54" s="5"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L55" s="1"/>
+      <c r="M55" s="5"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L56" s="1"/>
+      <c r="M56" s="5"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L57" s="1"/>
+      <c r="M57" s="5"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L58" s="1"/>
+      <c r="M58" s="5"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L59" s="1"/>
+      <c r="M59" s="5"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L60" s="1"/>
+      <c r="M60" s="5"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L61" s="1"/>
+      <c r="M61" s="5"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L62" s="1"/>
+      <c r="M62" s="5"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L63" s="1"/>
+      <c r="M63" s="5"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L64" s="1"/>
+      <c r="M64" s="5"/>
+    </row>
+    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="1"/>
+      <c r="M65" s="5"/>
+    </row>
+    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L66" s="1"/>
+      <c r="M66" s="5"/>
+    </row>
+    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L67" s="1"/>
+      <c r="M67" s="5"/>
+    </row>
+    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L68" s="1"/>
+      <c r="M68" s="5"/>
+    </row>
+    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L69" s="1"/>
+      <c r="M69" s="5"/>
+    </row>
+    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L70" s="1"/>
+      <c r="M70" s="5"/>
+    </row>
+    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L71" s="1"/>
+      <c r="M71" s="5"/>
+    </row>
+    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L72" s="1"/>
+      <c r="M72" s="5"/>
+    </row>
+    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L73" s="1"/>
+      <c r="M73" s="5"/>
+    </row>
+    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L74" s="1"/>
+      <c r="M74" s="5"/>
+    </row>
+    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L75" s="1"/>
+      <c r="M75" s="5"/>
+    </row>
+    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L76" s="1"/>
+      <c r="M76" s="5"/>
+    </row>
+    <row r="77" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L77" s="1"/>
+      <c r="M77" s="5"/>
+    </row>
+    <row r="78" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L78" s="1"/>
+      <c r="M78" s="5"/>
+    </row>
+    <row r="79" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L79" s="1"/>
+      <c r="M79" s="5"/>
+    </row>
+    <row r="80" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L80" s="1"/>
+      <c r="M80" s="5"/>
+    </row>
+    <row r="81" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L81" s="1"/>
+      <c r="M81" s="5"/>
+    </row>
+    <row r="82" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L82" s="1"/>
+      <c r="M82" s="5"/>
+    </row>
+    <row r="83" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L83" s="1"/>
+      <c r="M83" s="5"/>
+    </row>
+    <row r="84" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L84" s="1"/>
+      <c r="M84" s="5"/>
+    </row>
+    <row r="85" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L85" s="1"/>
+      <c r="M85" s="5"/>
+    </row>
+    <row r="86" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L86" s="1"/>
+      <c r="M86" s="5"/>
+    </row>
+    <row r="87" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L87" s="1"/>
+      <c r="M87" s="5"/>
+    </row>
+    <row r="88" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L88" s="1"/>
+      <c r="M88" s="5"/>
+    </row>
+    <row r="89" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L89" s="1"/>
+      <c r="M89" s="5"/>
+    </row>
+    <row r="90" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L90" s="1"/>
+      <c r="M90" s="5"/>
+    </row>
+    <row r="91" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L91" s="1"/>
+      <c r="M91" s="5"/>
+    </row>
+    <row r="92" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="1"/>
+      <c r="M92" s="5"/>
+    </row>
+    <row r="93" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L93" s="1"/>
+      <c r="M93" s="5"/>
+    </row>
+    <row r="94" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L94" s="1"/>
+      <c r="M94" s="5"/>
+    </row>
+    <row r="95" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L95" s="1"/>
+      <c r="M95" s="5"/>
+    </row>
+    <row r="96" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L96" s="1"/>
+      <c r="M96" s="5"/>
+    </row>
+    <row r="97" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L97" s="1"/>
+      <c r="M97" s="5"/>
+    </row>
+    <row r="98" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L98" s="1"/>
+      <c r="M98" s="5"/>
+    </row>
+    <row r="99" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L99" s="1"/>
+      <c r="M99" s="5"/>
+    </row>
+    <row r="100" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L100" s="1"/>
+      <c r="M100" s="5"/>
+    </row>
+    <row r="101" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L101" s="1"/>
+      <c r="M101" s="5"/>
+    </row>
+    <row r="102" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L102" s="1"/>
+      <c r="M102" s="5"/>
+    </row>
+    <row r="103" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L103" s="1"/>
+      <c r="M103" s="5"/>
+    </row>
+    <row r="104" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L104" s="1"/>
+      <c r="M104" s="5"/>
+    </row>
+    <row r="105" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L105" s="1"/>
+      <c r="M105" s="5"/>
+    </row>
+    <row r="106" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L106" s="1"/>
+      <c r="M106" s="5"/>
+    </row>
+    <row r="107" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L107" s="1"/>
+      <c r="M107" s="5"/>
+    </row>
+    <row r="108" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L108" s="1"/>
+      <c r="M108" s="5"/>
+    </row>
+    <row r="109" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L109" s="1"/>
+      <c r="M109" s="5"/>
+    </row>
+    <row r="110" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L110" s="1"/>
+      <c r="M110" s="5"/>
+    </row>
+    <row r="111" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L111" s="1"/>
+      <c r="M111" s="5"/>
+    </row>
+    <row r="112" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L112" s="1"/>
+      <c r="M112" s="5"/>
+    </row>
+    <row r="113" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L113" s="1"/>
+      <c r="M113" s="5"/>
+    </row>
+    <row r="114" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L114" s="1"/>
+      <c r="M114" s="5"/>
+    </row>
+    <row r="115" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L115" s="1"/>
+      <c r="M115" s="5"/>
+    </row>
+    <row r="116" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L116" s="1"/>
+      <c r="M116" s="5"/>
+    </row>
+    <row r="117" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="1"/>
+      <c r="M117" s="5"/>
+    </row>
+    <row r="118" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L118" s="1"/>
+      <c r="M118" s="5"/>
+    </row>
+    <row r="119" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L119" s="1"/>
+      <c r="M119" s="5"/>
+    </row>
+    <row r="120" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L120" s="1"/>
+      <c r="M120" s="5"/>
+    </row>
+    <row r="121" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L121" s="1"/>
+      <c r="M121" s="5"/>
+    </row>
+    <row r="122" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L122" s="1"/>
+      <c r="M122" s="5"/>
+    </row>
+    <row r="123" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L123" s="1"/>
+      <c r="M123" s="5"/>
+    </row>
+    <row r="124" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L124" s="1"/>
+      <c r="M124" s="5"/>
+    </row>
+    <row r="125" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L125" s="1"/>
+      <c r="M125" s="5"/>
+    </row>
+    <row r="126" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L126" s="1"/>
+      <c r="M126" s="5"/>
+    </row>
+    <row r="127" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L127" s="1"/>
+      <c r="M127" s="5"/>
+    </row>
+    <row r="128" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L128" s="1"/>
+      <c r="M128" s="5"/>
+    </row>
+    <row r="129" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L129" s="1"/>
+      <c r="M129" s="5"/>
+    </row>
+    <row r="130" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L130" s="1"/>
+      <c r="M130" s="5"/>
+    </row>
+    <row r="131" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L131" s="1"/>
+      <c r="M131" s="5"/>
+    </row>
+    <row r="132" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L132" s="1"/>
+      <c r="M132" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3086,11 +3443,12 @@
     <hyperlink ref="L51" r:id="rId47" xr:uid="{81DF7415-74A4-4A5B-BEF1-69F35D75A991}"/>
     <hyperlink ref="L52" r:id="rId48" xr:uid="{6D6C9EBD-C509-45AC-AD32-2A67AD2727AD}"/>
     <hyperlink ref="L53" r:id="rId49" xr:uid="{A01892A1-954B-41E4-B4CB-95523808FE8E}"/>
+    <hyperlink ref="L54" r:id="rId50" xr:uid="{5A52ABF7-103B-48A3-9933-A864844B57D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId50"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId51"/>
   <tableParts count="1">
-    <tablePart r:id="rId51"/>
+    <tablePart r:id="rId52"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215150F6-4860-4BB6-BF41-55F4F3B4897C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CEDE61-1C4A-4FFA-B421-47742D9ADF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3864" yWindow="1596" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="259">
   <si>
     <t>ID</t>
   </si>
@@ -780,6 +780,42 @@
   </si>
   <si>
     <t>Sosteniamo il Congresso di fondazione del PARTITO COMUNISTA (marxista-leninista) ITALIANO per fare l'Italia rossa e socialista come la Cina di Mao</t>
+  </si>
+  <si>
+    <t>AMI-0054</t>
+  </si>
+  <si>
+    <t>AMI-0055</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/manifesto-pcudi-breznev</t>
+  </si>
+  <si>
+    <t>manifesto-pcudi-breznev.jpg</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce</t>
+  </si>
+  <si>
+    <t>Manifesto</t>
+  </si>
+  <si>
+    <t>Linea Proletaria</t>
+  </si>
+  <si>
+    <t>Partito Comunista Unificato d'Italia</t>
+  </si>
+  <si>
+    <t>RICERCATO: Leonida Breznev - Manifesto del Partito Comunista Unificato d'Italia</t>
+  </si>
+  <si>
+    <t>Osare pensare, osare parlare, osare agire, osare fare la rivoluzione - Manifesto PCd'I (m-l)</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/osare-poster-pcdi</t>
+  </si>
+  <si>
+    <t>osare-poster-pcdi.png</t>
   </si>
 </sst>
 </file>
@@ -3080,12 +3116,74 @@
       <c r="M54" s="5"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L55" s="1"/>
-      <c r="M55" s="5"/>
+      <c r="A55" t="s">
+        <v>247</v>
+      </c>
+      <c r="B55" t="s">
+        <v>255</v>
+      </c>
+      <c r="C55" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" t="s">
+        <v>254</v>
+      </c>
+      <c r="E55" t="s">
+        <v>253</v>
+      </c>
+      <c r="F55">
+        <v>1978</v>
+      </c>
+      <c r="G55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H55" t="s">
+        <v>161</v>
+      </c>
+      <c r="I55" t="s">
+        <v>165</v>
+      </c>
+      <c r="J55" t="s">
+        <v>251</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L56" s="1"/>
-      <c r="M56" s="5"/>
+      <c r="A56" t="s">
+        <v>248</v>
+      </c>
+      <c r="B56" t="s">
+        <v>256</v>
+      </c>
+      <c r="C56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56">
+        <v>1967</v>
+      </c>
+      <c r="G56" t="s">
+        <v>252</v>
+      </c>
+      <c r="I56" t="s">
+        <v>165</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L57" s="1"/>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CEDE61-1C4A-4FFA-B421-47742D9ADF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E4B5E3-6365-47ED-B909-C36574E3EA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="267">
   <si>
     <t>ID</t>
   </si>
@@ -816,6 +816,30 @@
   </si>
   <si>
     <t>osare-poster-pcdi.png</t>
+  </si>
+  <si>
+    <t>AMI-0056</t>
+  </si>
+  <si>
+    <t>Il Presidente Mao Tse-tung sulla Guerra di popolo</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/mao-tse-tung-guerra-di-popolo/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0057</t>
+  </si>
+  <si>
+    <t>Congresso di fondazione del Partito Comunista d'Italia</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/fondazione-pcudi-1977</t>
+  </si>
+  <si>
+    <t>fondazione-pcudi-1977.jpg</t>
+  </si>
+  <si>
+    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) - Fronte Unito; Partito Comunista d'Italia (marxista-leninista) - Lotta di lunga; Partito Marxista-Leninista-Maoista Italiano</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1313,7 @@
     <col min="2" max="2" width="53.5546875" customWidth="1"/>
     <col min="3" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
     <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="10" max="10" width="22.44140625" customWidth="1"/>
@@ -3131,8 +3155,8 @@
       <c r="E55" t="s">
         <v>253</v>
       </c>
-      <c r="F55">
-        <v>1978</v>
+      <c r="F55" s="4">
+        <v>28550</v>
       </c>
       <c r="G55" t="s">
         <v>252</v>
@@ -3186,12 +3210,78 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L57" s="1"/>
+      <c r="A57" t="s">
+        <v>259</v>
+      </c>
+      <c r="B57" t="s">
+        <v>260</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>56</v>
+      </c>
+      <c r="F57">
+        <v>1967</v>
+      </c>
+      <c r="G57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" t="s">
+        <v>196</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="M57" s="5"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L58" s="1"/>
-      <c r="M58" s="5"/>
+      <c r="A58" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" t="s">
+        <v>254</v>
+      </c>
+      <c r="E58" t="s">
+        <v>253</v>
+      </c>
+      <c r="F58" s="3">
+        <v>28253</v>
+      </c>
+      <c r="G58" t="s">
+        <v>44</v>
+      </c>
+      <c r="H58" t="s">
+        <v>169</v>
+      </c>
+      <c r="I58" t="s">
+        <v>165</v>
+      </c>
+      <c r="J58" t="s">
+        <v>251</v>
+      </c>
+      <c r="K58" t="s">
+        <v>266</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L59" s="1"/>
@@ -3542,11 +3632,12 @@
     <hyperlink ref="L52" r:id="rId48" xr:uid="{6D6C9EBD-C509-45AC-AD32-2A67AD2727AD}"/>
     <hyperlink ref="L53" r:id="rId49" xr:uid="{A01892A1-954B-41E4-B4CB-95523808FE8E}"/>
     <hyperlink ref="L54" r:id="rId50" xr:uid="{5A52ABF7-103B-48A3-9933-A864844B57D6}"/>
+    <hyperlink ref="L57" r:id="rId51" xr:uid="{09F4A066-8FFE-45CF-800B-1E59F7E2C7C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId51"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId52"/>
   <tableParts count="1">
-    <tablePart r:id="rId52"/>
+    <tablePart r:id="rId53"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E4B5E3-6365-47ED-B909-C36574E3EA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9889F5D0-D2C1-4524-9904-27A56E52E1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
+    <workbookView xWindow="348" yWindow="3060" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -836,10 +836,10 @@
     <t>https://archive.org/details/fondazione-pcudi-1977</t>
   </si>
   <si>
-    <t>fondazione-pcudi-1977.jpg</t>
-  </si>
-  <si>
     <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) - Fronte Unito; Partito Comunista d'Italia (marxista-leninista) - Lotta di lunga; Partito Marxista-Leninista-Maoista Italiano</t>
+  </si>
+  <si>
+    <t>05.08.1977-fondazione-pcudi.png</t>
   </si>
 </sst>
 </file>
@@ -3274,13 +3274,13 @@
         <v>251</v>
       </c>
       <c r="K58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>264</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9889F5D0-D2C1-4524-9904-27A56E52E1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB79B241-F61F-4688-8816-F9A4B511AF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="348" yWindow="3060" windowWidth="17280" windowHeight="8880" xr2:uid="{F5AF1365-4D1F-4A73-8F23-4ABAB32F4B91}"/>
   </bookViews>
@@ -830,9 +830,6 @@
     <t>AMI-0057</t>
   </si>
   <si>
-    <t>Congresso di fondazione del Partito Comunista d'Italia</t>
-  </si>
-  <si>
     <t>https://archive.org/details/fondazione-pcudi-1977</t>
   </si>
   <si>
@@ -840,6 +837,9 @@
   </si>
   <si>
     <t>05.08.1977-fondazione-pcudi.png</t>
+  </si>
+  <si>
+    <t>Congresso di fondazione del Partito Comunista Unificato d'Italia</t>
   </si>
 </sst>
 </file>
@@ -3247,7 +3247,7 @@
         <v>262</v>
       </c>
       <c r="B58" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C58" t="s">
         <v>254</v>
@@ -3274,13 +3274,13 @@
         <v>251</v>
       </c>
       <c r="K58" t="s">
+        <v>264</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="M58" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="M58" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
